--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="进度" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="35">
   <si>
     <t>日期</t>
   </si>
@@ -761,7 +761,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -775,6 +775,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1185,9 +1188,9 @@
         <v>0.073794785349101</v>
       </c>
       <c r="I2" s="3">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3">
+        <v>0.15311004784689</v>
+      </c>
+      <c r="J2" s="5">
         <v>0</v>
       </c>
       <c r="K2" s="3">
@@ -1252,47 +1255,47 @@
       </c>
       <c r="I3" s="3">
         <f>SUM($B2:I2)</f>
-        <v>1</v>
+        <v>1.15311004784689</v>
       </c>
       <c r="J3" s="3">
         <f>SUM($B2:J2)</f>
-        <v>1</v>
+        <v>1.15311004784689</v>
       </c>
       <c r="K3" s="3">
         <f>SUM($B2:K2)</f>
-        <v>1</v>
+        <v>1.15311004784689</v>
       </c>
       <c r="L3" s="3">
         <f>SUM($B2:L2)</f>
-        <v>1</v>
+        <v>1.15311004784689</v>
       </c>
       <c r="M3" s="3">
         <f>SUM($B2:M2)</f>
-        <v>1</v>
+        <v>1.15311004784689</v>
       </c>
       <c r="N3" s="3">
         <f>SUM($B2:N2)</f>
-        <v>1</v>
+        <v>1.15311004784689</v>
       </c>
       <c r="O3" s="3">
         <f>SUM($B2:O2)</f>
-        <v>1</v>
+        <v>1.15311004784689</v>
       </c>
       <c r="P3" s="3">
         <f>SUM($B2:P2)</f>
-        <v>1</v>
+        <v>1.15311004784689</v>
       </c>
       <c r="Q3" s="3">
         <f>SUM($B2:Q2)</f>
-        <v>1</v>
+        <v>1.15311004784689</v>
       </c>
       <c r="R3" s="3">
         <f>SUM($B2:R2)</f>
-        <v>1</v>
+        <v>1.15311004784689</v>
       </c>
       <c r="S3" s="3">
         <f>SUM($B2:S2)</f>
-        <v>1</v>
+        <v>1.15311004784689</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1329,47 +1332,47 @@
       </c>
       <c r="I4" s="3">
         <f>AVERAGE($B2:I2)</f>
-        <v>0.125</v>
+        <v>0.144138755980861</v>
       </c>
       <c r="J4" s="3">
         <f>AVERAGE($B2:J2)</f>
-        <v>0.111111111111111</v>
+        <v>0.128123338649655</v>
       </c>
       <c r="K4" s="3">
         <f>AVERAGE($B2:K2)</f>
-        <v>0.1</v>
+        <v>0.115311004784689</v>
       </c>
       <c r="L4" s="3">
         <f>AVERAGE($B2:L2)</f>
-        <v>0.0909090909090909</v>
+        <v>0.104828186167899</v>
       </c>
       <c r="M4" s="3">
         <f>AVERAGE($B2:M2)</f>
-        <v>0.0833333333333333</v>
+        <v>0.0960925039872409</v>
       </c>
       <c r="N4" s="3">
         <f>AVERAGE($B2:N2)</f>
-        <v>0.0769230769230769</v>
+        <v>0.0887007729112993</v>
       </c>
       <c r="O4" s="3">
         <f>AVERAGE($B2:O2)</f>
-        <v>0.0714285714285714</v>
+        <v>0.0823650034176351</v>
       </c>
       <c r="P4" s="3">
         <f>AVERAGE($B2:P2)</f>
-        <v>0.0666666666666667</v>
+        <v>0.0768740031897927</v>
       </c>
       <c r="Q4" s="3">
         <f>AVERAGE($B2:Q2)</f>
-        <v>0.0625</v>
+        <v>0.0720693779904307</v>
       </c>
       <c r="R4" s="3">
         <f>AVERAGE($B2:R2)</f>
-        <v>0.0588235294117647</v>
+        <v>0.067830002814523</v>
       </c>
       <c r="S4" s="3">
         <f>AVERAGE($B2:S2)</f>
-        <v>0.0555555555555556</v>
+        <v>0.0640616693248273</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1455,35 +1458,35 @@
       </c>
       <c r="B6" s="3">
         <f t="shared" ref="B6:S6" si="1">B5-B2</f>
-        <v>-0.000521381928995979</v>
+        <v>-0.000521381928996006</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="1"/>
-        <v>-0.000521381928995979</v>
+        <v>-0.000521381928996006</v>
       </c>
       <c r="D6" s="3">
         <f t="shared" si="1"/>
-        <v>-0.000521381928995979</v>
+        <v>-0.000521381928996006</v>
       </c>
       <c r="E6" s="3">
         <f t="shared" si="1"/>
-        <v>-0.000521381928995979</v>
+        <v>-0.000521381928996006</v>
       </c>
       <c r="F6" s="3">
         <f t="shared" si="1"/>
-        <v>-0.000521381928995979</v>
+        <v>-0.000521381928996006</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" si="1"/>
-        <v>-0.000521381928995979</v>
+        <v>-0.000521381928996006</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="1"/>
-        <v>0.0800513684970529</v>
+        <v>0.080051368497053</v>
       </c>
       <c r="I6" s="3">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
+        <v>0.000736105999264047</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="1"/>
@@ -1693,7 +1696,7 @@
       <c r="H15" s="1">
         <v>240</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="6">
         <f t="shared" ref="I15:I20" si="5">MIN($J$14*D15,J15)</f>
         <v>257</v>
       </c>
@@ -1731,7 +1734,7 @@
       <c r="H16" s="1">
         <v>360</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="6">
         <f t="shared" si="5"/>
         <v>390</v>
       </c>
@@ -1769,7 +1772,7 @@
       <c r="H17" s="1">
         <v>444</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="6">
         <f t="shared" si="5"/>
         <v>484</v>
       </c>
@@ -1807,7 +1810,7 @@
       <c r="H18" s="1">
         <v>222</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="6">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
@@ -1845,7 +1848,7 @@
       <c r="H19" s="1">
         <v>252</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="6">
         <f t="shared" si="5"/>
         <v>271</v>
       </c>
@@ -1883,7 +1886,7 @@
       <c r="H20" s="1">
         <v>258</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="6">
         <f t="shared" si="5"/>
         <v>278</v>
       </c>
@@ -1933,7 +1936,7 @@
         <v>15</v>
       </c>
       <c r="J23" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1963,9 +1966,12 @@
         <f>I24-H24</f>
         <v>68</v>
       </c>
+      <c r="H24" s="1">
+        <v>68</v>
+      </c>
       <c r="I24" s="6">
         <f>MIN($J$23*D24,J24)</f>
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="J24" s="1">
         <v>322</v>
@@ -1988,19 +1994,22 @@
       </c>
       <c r="E25" s="3">
         <f>AVERAGE(F25:F$26)</f>
-        <v>0.0767195767195767</v>
+        <v>0.0921179210652895</v>
       </c>
       <c r="F25" s="3">
         <f>G25/B25</f>
-        <v>0.153439153439153</v>
+        <v>0.0502645502645503</v>
       </c>
       <c r="G25" s="1">
         <f>I25-H25</f>
+        <v>19</v>
+      </c>
+      <c r="H25" s="1">
         <v>58</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="7">
         <f>MIN($J$23*D25,J25)</f>
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="J25" s="1">
         <v>77</v>
@@ -2023,22 +2032,25 @@
       </c>
       <c r="E26" s="3">
         <f>AVERAGE(F26:F$26)</f>
-        <v>0</v>
+        <v>0.133971291866029</v>
       </c>
       <c r="F26" s="3">
         <f>G26/B26</f>
-        <v>0</v>
+        <v>0.133971291866029</v>
       </c>
       <c r="G26" s="1">
         <f>I26-H26</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="6">
+        <v>28</v>
+      </c>
+      <c r="H26" s="1">
+        <v>32</v>
+      </c>
+      <c r="I26" s="7">
         <f>MIN($J$23*D26,J26)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J26" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2077,13 +2089,16 @@
       <c r="I29" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="C30" s="3">
         <f>4/26</f>
@@ -2091,22 +2106,26 @@
       </c>
       <c r="D30" s="1">
         <f t="shared" ref="D30:D36" si="7">ROUND(B30*C30,0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E30" s="3">
         <f>AVERAGE(F$30:F30)</f>
-        <v>0</v>
+        <v>0.161290322580645</v>
       </c>
       <c r="F30" s="3">
         <f t="shared" ref="F30:F35" si="8">G30/B30</f>
-        <v>0</v>
+        <v>0.161290322580645</v>
       </c>
       <c r="G30" s="1">
         <f t="shared" ref="G30:G35" si="9">I30-H30</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="1">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="I30" s="6">
+        <f>MIN($J$29*D30,J30)</f>
+        <v>10</v>
+      </c>
+      <c r="J30" s="1">
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2114,7 +2133,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>1</v>
+        <v>464</v>
       </c>
       <c r="C31" s="3">
         <f>C30</f>
@@ -2122,11 +2141,11 @@
       </c>
       <c r="D31" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="E31" s="3">
         <f>AVERAGE(F$30:F31)</f>
-        <v>0</v>
+        <v>0.0806451612903226</v>
       </c>
       <c r="F31" s="3">
         <f t="shared" si="8"/>
@@ -2137,6 +2156,9 @@
         <v>0</v>
       </c>
       <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2213,7 +2235,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="J2:S2 A1:S1 A2 A3:S8 A9:D9 A10:C11 A12:D14 K9:S20 C15:D16 A16 A17:D20" formulaRange="1"/>
+    <ignoredError sqref="A17:D20 A16 C15:D16 K9:S20 A12:D14 A10:C11 A9:D9 A3:S8 A2 A1:S1 J2:S2" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2221,7 +2243,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="10.7777777777778" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="16384" width="10.7777777777778" style="1" customWidth="1"/>
@@ -2303,6 +2325,25 @@
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="B11" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -1994,7 +1994,7 @@
       </c>
       <c r="E25" s="3">
         <f>AVERAGE(F25:F$26)</f>
-        <v>0.0921179210652895</v>
+        <v>0.10168729905572</v>
       </c>
       <c r="F25" s="3">
         <f>G25/B25</f>
@@ -2032,25 +2032,25 @@
       </c>
       <c r="E26" s="3">
         <f>AVERAGE(F26:F$26)</f>
-        <v>0.133971291866029</v>
+        <v>0.15311004784689</v>
       </c>
       <c r="F26" s="3">
         <f>G26/B26</f>
-        <v>0.133971291866029</v>
+        <v>0.15311004784689</v>
       </c>
       <c r="G26" s="1">
         <f>I26-H26</f>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H26" s="1">
         <v>32</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I26" s="6">
         <f>MIN($J$23*D26,J26)</f>
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J26" s="1">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2235,7 +2235,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A17:D20 A16 C15:D16 K9:S20 A12:D14 A10:C11 A9:D9 A3:S8 A2 A1:S1 J2:S2" formulaRange="1"/>
+    <ignoredError sqref="J2:S2 A1:S1 A2 A3:S8 A9:D9 A10:C11 A12:D14 K9:S20 C15:D16 A16 A17:D20" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2326,7 +2326,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="1">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:2">

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="37">
   <si>
     <t>日期</t>
   </si>
@@ -105,7 +105,7 @@
     <t>契约设计</t>
   </si>
   <si>
-    <t>计组复试</t>
+    <t>系统组成</t>
   </si>
   <si>
     <t>计算历史</t>
@@ -117,19 +117,25 @@
     <t>逆向工程</t>
   </si>
   <si>
-    <t>系统工作</t>
-  </si>
-  <si>
     <t>实时调度</t>
   </si>
   <si>
     <t>安卓移植</t>
   </si>
   <si>
-    <t>网络经验</t>
+    <t>复试网络</t>
+  </si>
+  <si>
+    <t>农大上机</t>
+  </si>
+  <si>
+    <t>农大面试</t>
   </si>
   <si>
     <t>华为认证</t>
+  </si>
+  <si>
+    <t>简历处理</t>
   </si>
   <si>
     <t>页码</t>
@@ -1187,8 +1193,8 @@
       <c r="H2" s="3">
         <v>0.073794785349101</v>
       </c>
-      <c r="I2" s="3">
-        <v>0.15311004784689</v>
+      <c r="I2" s="5">
+        <v>0</v>
       </c>
       <c r="J2" s="5">
         <v>0</v>
@@ -1255,47 +1261,47 @@
       </c>
       <c r="I3" s="3">
         <f>SUM($B2:I2)</f>
-        <v>1.15311004784689</v>
+        <v>1</v>
       </c>
       <c r="J3" s="3">
         <f>SUM($B2:J2)</f>
-        <v>1.15311004784689</v>
+        <v>1</v>
       </c>
       <c r="K3" s="3">
         <f>SUM($B2:K2)</f>
-        <v>1.15311004784689</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3">
         <f>SUM($B2:L2)</f>
-        <v>1.15311004784689</v>
+        <v>1</v>
       </c>
       <c r="M3" s="3">
         <f>SUM($B2:M2)</f>
-        <v>1.15311004784689</v>
+        <v>1</v>
       </c>
       <c r="N3" s="3">
         <f>SUM($B2:N2)</f>
-        <v>1.15311004784689</v>
+        <v>1</v>
       </c>
       <c r="O3" s="3">
         <f>SUM($B2:O2)</f>
-        <v>1.15311004784689</v>
+        <v>1</v>
       </c>
       <c r="P3" s="3">
         <f>SUM($B2:P2)</f>
-        <v>1.15311004784689</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="3">
         <f>SUM($B2:Q2)</f>
-        <v>1.15311004784689</v>
+        <v>1</v>
       </c>
       <c r="R3" s="3">
         <f>SUM($B2:R2)</f>
-        <v>1.15311004784689</v>
+        <v>1</v>
       </c>
       <c r="S3" s="3">
         <f>SUM($B2:S2)</f>
-        <v>1.15311004784689</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1332,47 +1338,47 @@
       </c>
       <c r="I4" s="3">
         <f>AVERAGE($B2:I2)</f>
-        <v>0.144138755980861</v>
+        <v>0.125</v>
       </c>
       <c r="J4" s="3">
         <f>AVERAGE($B2:J2)</f>
-        <v>0.128123338649655</v>
+        <v>0.111111111111111</v>
       </c>
       <c r="K4" s="3">
         <f>AVERAGE($B2:K2)</f>
-        <v>0.115311004784689</v>
+        <v>0.1</v>
       </c>
       <c r="L4" s="3">
         <f>AVERAGE($B2:L2)</f>
-        <v>0.104828186167899</v>
+        <v>0.090909090909091</v>
       </c>
       <c r="M4" s="3">
         <f>AVERAGE($B2:M2)</f>
-        <v>0.0960925039872409</v>
+        <v>0.0833333333333334</v>
       </c>
       <c r="N4" s="3">
         <f>AVERAGE($B2:N2)</f>
-        <v>0.0887007729112993</v>
+        <v>0.076923076923077</v>
       </c>
       <c r="O4" s="3">
         <f>AVERAGE($B2:O2)</f>
-        <v>0.0823650034176351</v>
+        <v>0.0714285714285715</v>
       </c>
       <c r="P4" s="3">
         <f>AVERAGE($B2:P2)</f>
-        <v>0.0768740031897927</v>
+        <v>0.0666666666666667</v>
       </c>
       <c r="Q4" s="3">
         <f>AVERAGE($B2:Q2)</f>
-        <v>0.0720693779904307</v>
+        <v>0.0625000000000001</v>
       </c>
       <c r="R4" s="3">
         <f>AVERAGE($B2:R2)</f>
-        <v>0.067830002814523</v>
+        <v>0.0588235294117648</v>
       </c>
       <c r="S4" s="3">
         <f>AVERAGE($B2:S2)</f>
-        <v>0.0640616693248273</v>
+        <v>0.0555555555555556</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1486,7 +1492,7 @@
       </c>
       <c r="I6" s="3">
         <f t="shared" si="1"/>
-        <v>0.000736105999264047</v>
+        <v>0.153846153846154</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="1"/>
@@ -1936,7 +1942,7 @@
         <v>15</v>
       </c>
       <c r="J23" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1951,27 +1957,24 @@
         <v>0.153846153846154</v>
       </c>
       <c r="D24" s="1">
-        <f>ROUND(B24*C24,0)</f>
+        <f t="shared" ref="D24:D28" si="7">ROUND(B24*C24,0)</f>
         <v>68</v>
       </c>
       <c r="E24" s="3">
-        <f>AVERAGE(F$15:F24)</f>
-        <v>0.0853305952342944</v>
+        <f>AVERAGE(F$24:F24)</f>
+        <v>0.154545454545455</v>
       </c>
       <c r="F24" s="3">
-        <f>G24/B24</f>
+        <f t="shared" ref="F24:F28" si="8">G24/B24</f>
         <v>0.154545454545455</v>
       </c>
       <c r="G24" s="1">
-        <f>I24-H24</f>
+        <f t="shared" ref="G24:G28" si="9">I24-H24</f>
         <v>68</v>
       </c>
-      <c r="H24" s="1">
+      <c r="I24" s="6">
+        <f t="shared" ref="I24:I28" si="10">MIN($J$23*D24,J24)</f>
         <v>68</v>
-      </c>
-      <c r="I24" s="6">
-        <f>MIN($J$23*D24,J24)</f>
-        <v>136</v>
       </c>
       <c r="J24" s="1">
         <v>322</v>
@@ -1985,31 +1988,28 @@
         <v>378</v>
       </c>
       <c r="C25" s="3">
-        <f>C24</f>
+        <f t="shared" ref="C25:C28" si="11">C24</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D25" s="1">
-        <f>ROUND(B25*C25,0)</f>
+        <f t="shared" si="7"/>
         <v>58</v>
       </c>
       <c r="E25" s="3">
-        <f>AVERAGE(F25:F$26)</f>
-        <v>0.10168729905572</v>
+        <f>AVERAGE(F$24:F25)</f>
+        <v>0.153992303992304</v>
       </c>
       <c r="F25" s="3">
-        <f>G25/B25</f>
-        <v>0.0502645502645503</v>
+        <f t="shared" si="8"/>
+        <v>0.153439153439153</v>
       </c>
       <c r="G25" s="1">
-        <f>I25-H25</f>
-        <v>19</v>
-      </c>
-      <c r="H25" s="1">
+        <f t="shared" si="9"/>
         <v>58</v>
       </c>
-      <c r="I25" s="7">
-        <f>MIN($J$23*D25,J25)</f>
-        <v>77</v>
+      <c r="I25" s="6">
+        <f t="shared" si="10"/>
+        <v>58</v>
       </c>
       <c r="J25" s="1">
         <v>77</v>
@@ -2023,211 +2023,289 @@
         <v>209</v>
       </c>
       <c r="C26" s="3">
-        <f>C25</f>
+        <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D26" s="1">
-        <f>ROUND(B26*C26,0)</f>
+        <f t="shared" si="7"/>
         <v>32</v>
       </c>
       <c r="E26" s="3">
-        <f>AVERAGE(F26:F$26)</f>
+        <f>AVERAGE(F$24:F26)</f>
+        <v>0.153698218610499</v>
+      </c>
+      <c r="F26" s="3">
+        <f t="shared" si="8"/>
         <v>0.15311004784689</v>
       </c>
-      <c r="F26" s="3">
-        <f>G26/B26</f>
-        <v>0.15311004784689</v>
-      </c>
       <c r="G26" s="1">
-        <f>I26-H26</f>
+        <f t="shared" si="9"/>
         <v>32</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="6">
+        <f t="shared" si="10"/>
         <v>32</v>
-      </c>
-      <c r="I26" s="6">
-        <f>MIN($J$23*D26,J26)</f>
-        <v>64</v>
       </c>
       <c r="J26" s="1">
         <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="C27" s="3"/>
+      <c r="A27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="1">
+        <v>62</v>
+      </c>
+      <c r="C27" s="3">
+        <f t="shared" si="11"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D27" s="1">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="E27" s="3">
+        <f>AVERAGE(F$24:F27)</f>
+        <v>0.155596244603036</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" si="8"/>
+        <v>0.161290322580645</v>
+      </c>
+      <c r="G27" s="1">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+      <c r="I27" s="6">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="J27" s="1">
+        <v>40</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="B28" s="1">
+        <v>464</v>
+      </c>
+      <c r="C28" s="3">
+        <f t="shared" si="11"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D28" s="1">
+        <f t="shared" si="7"/>
+        <v>71</v>
+      </c>
+      <c r="E28" s="3">
+        <f>AVERAGE(F$24:F28)</f>
+        <v>0.124476995682429</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="1">
-        <v>1</v>
-      </c>
+      <c r="C29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="1">
-        <v>62</v>
-      </c>
-      <c r="C30" s="3">
-        <f>4/26</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="D30" s="1">
-        <f t="shared" ref="D30:D36" si="7">ROUND(B30*C30,0)</f>
-        <v>10</v>
-      </c>
-      <c r="E30" s="3">
-        <f>AVERAGE(F$30:F30)</f>
-        <v>0.161290322580645</v>
-      </c>
-      <c r="F30" s="3">
-        <f t="shared" ref="F30:F35" si="8">G30/B30</f>
-        <v>0.161290322580645</v>
-      </c>
-      <c r="G30" s="1">
-        <f t="shared" ref="G30:G35" si="9">I30-H30</f>
-        <v>10</v>
-      </c>
-      <c r="I30" s="6">
-        <f>MIN($J$29*D30,J30)</f>
-        <v>10</v>
-      </c>
-      <c r="J30" s="1">
-        <v>40</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="1">
-        <v>464</v>
-      </c>
-      <c r="C31" s="3">
-        <f>C30</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="D31" s="1">
-        <f t="shared" si="7"/>
-        <v>71</v>
-      </c>
-      <c r="E31" s="3">
-        <f>AVERAGE(F$30:F31)</f>
-        <v>0.0806451612903226</v>
-      </c>
-      <c r="F31" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="1">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="J31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="1">
+        <v>177</v>
+      </c>
+      <c r="C32" s="3">
+        <f>4/26</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D32" s="1">
+        <f>ROUND(B32*C32,0)</f>
+        <v>27</v>
+      </c>
+      <c r="E32" s="3">
+        <f>AVERAGE(F$32:F32)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <f>G32/B32</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <f>I32-H32</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="6">
+        <f t="shared" ref="I32:I35" si="12">MIN($J$31*D32,J32)</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>33</v>
+      </c>
+      <c r="B33" s="1">
+        <v>212</v>
+      </c>
+      <c r="C33" s="3">
+        <f t="shared" ref="C33:C35" si="13">C32</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D33" s="1">
+        <f>ROUND(B33*C33,0)</f>
+        <v>33</v>
+      </c>
+      <c r="E33" s="3">
+        <f>AVERAGE(F$32:F33)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
+        <f>G33/B33</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <f>I33-H33</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="6">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="1">
+        <v>100</v>
+      </c>
+      <c r="C34" s="3">
+        <f t="shared" si="13"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D34" s="1">
+        <f>ROUND(B34*C34,0)</f>
         <v>15</v>
       </c>
-    </row>
-    <row r="35" spans="1:9">
+      <c r="E34" s="3">
+        <f>AVERAGE(F$32:F34)</f>
+        <v>0.05</v>
+      </c>
+      <c r="F34" s="3">
+        <f>G34/B34</f>
+        <v>0.15</v>
+      </c>
+      <c r="G34" s="1">
+        <f>I34-H34</f>
+        <v>15</v>
+      </c>
+      <c r="I34" s="6">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="J34" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B35" s="1">
         <v>1</v>
       </c>
       <c r="C35" s="3">
-        <f>4/26</f>
+        <f t="shared" si="13"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" si="7"/>
+        <f>ROUND(B35*C35,0)</f>
         <v>0</v>
       </c>
       <c r="E35" s="3">
-        <f>AVERAGE(F$35:F35)</f>
-        <v>0</v>
+        <f>AVERAGE(F$32:F35)</f>
+        <v>0.0375</v>
       </c>
       <c r="F35" s="3">
-        <f t="shared" si="8"/>
+        <f>G35/B35</f>
         <v>0</v>
       </c>
       <c r="G35" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <f>I35-H35</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="6">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="C36" s="3"/>
     </row>
   </sheetData>
@@ -2243,7 +2321,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="10.7777777777778" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="16384" width="10.7777777777778" style="1" customWidth="1"/>
@@ -2254,7 +2332,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2329,19 +2407,51 @@
         <v>66</v>
       </c>
     </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1">
+        <v>40</v>
+      </c>
+    </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B13" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="1">
         <v>0</v>
       </c>
     </row>

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -767,7 +767,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -781,9 +781,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1193,11 +1190,11 @@
       <c r="H2" s="3">
         <v>0.073794785349101</v>
       </c>
-      <c r="I2" s="5">
-        <v>0</v>
-      </c>
-      <c r="J2" s="5">
-        <v>0</v>
+      <c r="I2" s="4">
+        <v>0.155080443958291</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0.155080443958291</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -1261,47 +1258,47 @@
       </c>
       <c r="I3" s="3">
         <f>SUM($B2:I2)</f>
-        <v>1</v>
+        <v>1.15508044395829</v>
       </c>
       <c r="J3" s="3">
         <f>SUM($B2:J2)</f>
-        <v>1</v>
+        <v>1.31016088791658</v>
       </c>
       <c r="K3" s="3">
         <f>SUM($B2:K2)</f>
-        <v>1</v>
+        <v>1.31016088791658</v>
       </c>
       <c r="L3" s="3">
         <f>SUM($B2:L2)</f>
-        <v>1</v>
+        <v>1.31016088791658</v>
       </c>
       <c r="M3" s="3">
         <f>SUM($B2:M2)</f>
-        <v>1</v>
+        <v>1.31016088791658</v>
       </c>
       <c r="N3" s="3">
         <f>SUM($B2:N2)</f>
-        <v>1</v>
+        <v>1.31016088791658</v>
       </c>
       <c r="O3" s="3">
         <f>SUM($B2:O2)</f>
-        <v>1</v>
+        <v>1.31016088791658</v>
       </c>
       <c r="P3" s="3">
         <f>SUM($B2:P2)</f>
-        <v>1</v>
+        <v>1.31016088791658</v>
       </c>
       <c r="Q3" s="3">
         <f>SUM($B2:Q2)</f>
-        <v>1</v>
+        <v>1.31016088791658</v>
       </c>
       <c r="R3" s="3">
         <f>SUM($B2:R2)</f>
-        <v>1</v>
+        <v>1.31016088791658</v>
       </c>
       <c r="S3" s="3">
         <f>SUM($B2:S2)</f>
-        <v>1</v>
+        <v>1.31016088791658</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1338,47 +1335,47 @@
       </c>
       <c r="I4" s="3">
         <f>AVERAGE($B2:I2)</f>
-        <v>0.125</v>
+        <v>0.144385055494786</v>
       </c>
       <c r="J4" s="3">
         <f>AVERAGE($B2:J2)</f>
-        <v>0.111111111111111</v>
+        <v>0.145573431990731</v>
       </c>
       <c r="K4" s="3">
         <f>AVERAGE($B2:K2)</f>
-        <v>0.1</v>
+        <v>0.131016088791658</v>
       </c>
       <c r="L4" s="3">
         <f>AVERAGE($B2:L2)</f>
-        <v>0.090909090909091</v>
+        <v>0.119105535265144</v>
       </c>
       <c r="M4" s="3">
         <f>AVERAGE($B2:M2)</f>
-        <v>0.0833333333333334</v>
+        <v>0.109180073993049</v>
       </c>
       <c r="N4" s="3">
         <f>AVERAGE($B2:N2)</f>
-        <v>0.076923076923077</v>
+        <v>0.100781606762814</v>
       </c>
       <c r="O4" s="3">
         <f>AVERAGE($B2:O2)</f>
-        <v>0.0714285714285715</v>
+        <v>0.0935829205654702</v>
       </c>
       <c r="P4" s="3">
         <f>AVERAGE($B2:P2)</f>
-        <v>0.0666666666666667</v>
+        <v>0.0873440591944388</v>
       </c>
       <c r="Q4" s="3">
         <f>AVERAGE($B2:Q2)</f>
-        <v>0.0625000000000001</v>
+        <v>0.0818850554947864</v>
       </c>
       <c r="R4" s="3">
         <f>AVERAGE($B2:R2)</f>
-        <v>0.0588235294117648</v>
+        <v>0.0770682875245048</v>
       </c>
       <c r="S4" s="3">
         <f>AVERAGE($B2:S2)</f>
-        <v>0.0555555555555556</v>
+        <v>0.0727867159953657</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1492,11 +1489,11 @@
       </c>
       <c r="I6" s="3">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
+        <v>-0.00123429011213669</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
+        <v>-0.00123429011213669</v>
       </c>
       <c r="K6" s="3">
         <f t="shared" si="1"/>
@@ -1702,7 +1699,7 @@
       <c r="H15" s="1">
         <v>240</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="5">
         <f t="shared" ref="I15:I20" si="5">MIN($J$14*D15,J15)</f>
         <v>257</v>
       </c>
@@ -1740,7 +1737,7 @@
       <c r="H16" s="1">
         <v>360</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="5">
         <f t="shared" si="5"/>
         <v>390</v>
       </c>
@@ -1778,7 +1775,7 @@
       <c r="H17" s="1">
         <v>444</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="5">
         <f t="shared" si="5"/>
         <v>484</v>
       </c>
@@ -1816,7 +1813,7 @@
       <c r="H18" s="1">
         <v>222</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="5">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
@@ -1854,7 +1851,7 @@
       <c r="H19" s="1">
         <v>252</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="5">
         <f t="shared" si="5"/>
         <v>271</v>
       </c>
@@ -1892,7 +1889,7 @@
       <c r="H20" s="1">
         <v>258</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="5">
         <f t="shared" si="5"/>
         <v>278</v>
       </c>
@@ -1942,7 +1939,7 @@
         <v>15</v>
       </c>
       <c r="J23" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1972,9 +1969,12 @@
         <f t="shared" ref="G24:G28" si="9">I24-H24</f>
         <v>68</v>
       </c>
-      <c r="I24" s="6">
+      <c r="H24" s="1">
+        <v>136</v>
+      </c>
+      <c r="I24" s="5">
         <f t="shared" ref="I24:I28" si="10">MIN($J$23*D24,J24)</f>
-        <v>68</v>
+        <v>204</v>
       </c>
       <c r="J24" s="1">
         <v>322</v>
@@ -1997,22 +1997,25 @@
       </c>
       <c r="E25" s="3">
         <f>AVERAGE(F$24:F25)</f>
-        <v>0.153992303992304</v>
+        <v>0.0865319865319865</v>
       </c>
       <c r="F25" s="3">
         <f t="shared" si="8"/>
-        <v>0.153439153439153</v>
+        <v>0.0185185185185185</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" si="9"/>
-        <v>58</v>
+        <v>7</v>
+      </c>
+      <c r="H25" s="1">
+        <v>116</v>
       </c>
       <c r="I25" s="6">
         <f t="shared" si="10"/>
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="J25" s="1">
-        <v>77</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2032,19 +2035,22 @@
       </c>
       <c r="E26" s="3">
         <f>AVERAGE(F$24:F26)</f>
-        <v>0.153698218610499</v>
+        <v>0.0608777836848012</v>
       </c>
       <c r="F26" s="3">
         <f t="shared" si="8"/>
-        <v>0.15311004784689</v>
+        <v>0.00956937799043062</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="9"/>
-        <v>32</v>
+        <v>2</v>
+      </c>
+      <c r="H26" s="1">
+        <v>64</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="10"/>
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="J26" s="1">
         <v>66</v>
@@ -2067,7 +2073,7 @@
       </c>
       <c r="E27" s="3">
         <f>AVERAGE(F$24:F27)</f>
-        <v>0.155596244603036</v>
+        <v>0.0859809184087622</v>
       </c>
       <c r="F27" s="3">
         <f t="shared" si="8"/>
@@ -2077,9 +2083,12 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="I27" s="6">
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J27" s="1">
         <v>40</v>
@@ -2102,22 +2111,25 @@
       </c>
       <c r="E28" s="3">
         <f>AVERAGE(F$24:F28)</f>
-        <v>0.124476995682429</v>
+        <v>0.0726640450718374</v>
       </c>
       <c r="F28" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.0193965517241379</v>
       </c>
       <c r="G28" s="1">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="7">
+        <v>9</v>
+      </c>
+      <c r="H28" s="1">
+        <v>142</v>
+      </c>
+      <c r="I28" s="6">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="J28" s="1">
-        <v>0</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2192,7 +2204,7 @@
         <f>I32-H32</f>
         <v>0</v>
       </c>
-      <c r="I32" s="6">
+      <c r="I32" s="5">
         <f t="shared" ref="I32:I35" si="12">MIN($J$31*D32,J32)</f>
         <v>0</v>
       </c>
@@ -2227,7 +2239,7 @@
         <f>I33-H33</f>
         <v>0</v>
       </c>
-      <c r="I33" s="6">
+      <c r="I33" s="5">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -2262,7 +2274,7 @@
         <f>I34-H34</f>
         <v>15</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="5">
         <f t="shared" si="12"/>
         <v>15</v>
       </c>
@@ -2297,7 +2309,7 @@
         <f>I35-H35</f>
         <v>0</v>
       </c>
-      <c r="I35" s="6">
+      <c r="I35" s="5">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -2313,7 +2325,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="J2:S2 A1:S1 A2 A3:S8 A9:D9 A10:C11 A12:D14 K9:S20 C15:D16 A16 A17:D20" formulaRange="1"/>
+    <ignoredError sqref="K2:S2 A1:S1 A2 A3:S8 A9:D9 A10:C11 A12:D14 K9:S20 C15:D16 A16 A17:D20" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2396,7 +2408,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="1">
-        <v>77</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2420,7 +2432,7 @@
         <v>30</v>
       </c>
       <c r="B13" s="1">
-        <v>0</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:2">

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -2035,25 +2035,25 @@
       </c>
       <c r="E26" s="3">
         <f>AVERAGE(F$24:F26)</f>
-        <v>0.0608777836848012</v>
+        <v>0.0895859176560931</v>
       </c>
       <c r="F26" s="3">
         <f t="shared" si="8"/>
-        <v>0.00956937799043062</v>
+        <v>0.0956937799043062</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H26" s="1">
         <v>64</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="10"/>
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="J26" s="1">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="E27" s="3">
         <f>AVERAGE(F$24:F27)</f>
-        <v>0.0859809184087622</v>
+        <v>0.107512018887231</v>
       </c>
       <c r="F27" s="3">
         <f t="shared" si="8"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E28" s="3">
         <f>AVERAGE(F$24:F28)</f>
-        <v>0.0726640450718374</v>
+        <v>0.0898889254546125</v>
       </c>
       <c r="F28" s="3">
         <f t="shared" si="8"/>
@@ -2416,7 +2416,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="1">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:2">

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="进度" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="61">
   <si>
     <t>日期</t>
   </si>
@@ -105,7 +105,7 @@
     <t>契约设计</t>
   </si>
   <si>
-    <t>系统组成</t>
+    <t>计算组成</t>
   </si>
   <si>
     <t>计算历史</t>
@@ -123,22 +123,94 @@
     <t>安卓移植</t>
   </si>
   <si>
-    <t>复试网络</t>
-  </si>
-  <si>
-    <t>农大上机</t>
-  </si>
-  <si>
-    <t>农大面试</t>
+    <t>操作系统</t>
+  </si>
+  <si>
+    <t>安卓框架</t>
+  </si>
+  <si>
+    <t>系统建模</t>
+  </si>
+  <si>
+    <t>可靠系统</t>
+  </si>
+  <si>
+    <t>系统理论</t>
+  </si>
+  <si>
+    <t>网络安全</t>
   </si>
   <si>
     <t>华为认证</t>
   </si>
   <si>
-    <t>简历处理</t>
+    <t>渗透测试</t>
+  </si>
+  <si>
+    <t>复试针对</t>
+  </si>
+  <si>
+    <t>农大辅导</t>
+  </si>
+  <si>
+    <t>农大准备</t>
   </si>
   <si>
     <t>页码</t>
+  </si>
+  <si>
+    <t>简历</t>
+  </si>
+  <si>
+    <t>导师</t>
+  </si>
+  <si>
+    <t>LMS</t>
+  </si>
+  <si>
+    <t>CDCGAN</t>
+  </si>
+  <si>
+    <t>LabVIEW</t>
+  </si>
+  <si>
+    <t>OpenCog</t>
+  </si>
+  <si>
+    <t>OpenNARS</t>
+  </si>
+  <si>
+    <t>YOLO</t>
+  </si>
+  <si>
+    <t>FaceNet</t>
+  </si>
+  <si>
+    <t>BCI</t>
+  </si>
+  <si>
+    <t>MedImg</t>
+  </si>
+  <si>
+    <t>BioInfo</t>
+  </si>
+  <si>
+    <t>三论概述</t>
+  </si>
+  <si>
+    <t>面试</t>
+  </si>
+  <si>
+    <t>上机</t>
+  </si>
+  <si>
+    <t>视频</t>
+  </si>
+  <si>
+    <t>视频#</t>
+  </si>
+  <si>
+    <t>1-6</t>
   </si>
 </sst>
 </file>
@@ -767,11 +839,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1100,7 +1175,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="15.7777777777778" style="1" customWidth="1"/>
@@ -1110,58 +1185,58 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="3">
         <v>46081</v>
       </c>
-      <c r="C1" s="2">
+      <c r="C1" s="3">
         <v>46082</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="3">
         <v>46083</v>
       </c>
-      <c r="E1" s="2">
+      <c r="E1" s="3">
         <v>46084</v>
       </c>
-      <c r="F1" s="2">
+      <c r="F1" s="3">
         <v>46085</v>
       </c>
-      <c r="G1" s="2">
+      <c r="G1" s="3">
         <v>46086</v>
       </c>
-      <c r="H1" s="2">
+      <c r="H1" s="3">
         <v>46087</v>
       </c>
-      <c r="I1" s="2">
+      <c r="I1" s="3">
         <v>46088</v>
       </c>
-      <c r="J1" s="2">
+      <c r="J1" s="3">
         <v>46089</v>
       </c>
-      <c r="K1" s="2">
+      <c r="K1" s="3">
         <v>46090</v>
       </c>
-      <c r="L1" s="2">
+      <c r="L1" s="3">
         <v>46091</v>
       </c>
-      <c r="M1" s="2">
+      <c r="M1" s="3">
         <v>46092</v>
       </c>
-      <c r="N1" s="2">
+      <c r="N1" s="3">
         <v>46093</v>
       </c>
-      <c r="O1" s="2">
+      <c r="O1" s="3">
         <v>46094</v>
       </c>
-      <c r="P1" s="2">
+      <c r="P1" s="3">
         <v>46095</v>
       </c>
-      <c r="Q1" s="2">
+      <c r="Q1" s="3">
         <v>46096</v>
       </c>
-      <c r="R1" s="2">
+      <c r="R1" s="3">
         <v>46097</v>
       </c>
-      <c r="S1" s="2">
+      <c r="S1" s="3">
         <v>46098</v>
       </c>
     </row>
@@ -1169,58 +1244,58 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>0.15436753577515</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="4">
         <v>0.15436753577515</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="4">
         <v>0.15436753577515</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="4">
         <v>0.15436753577515</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="4">
         <v>0.15436753577515</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="5">
         <v>0.15436753577515</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="4">
         <v>0.073794785349101</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="5">
         <v>0.155080443958291</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="5">
         <v>0.155080443958291</v>
       </c>
-      <c r="K2" s="3">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3">
-        <v>0</v>
-      </c>
-      <c r="N2" s="3">
-        <v>0</v>
-      </c>
-      <c r="O2" s="3">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>0</v>
-      </c>
-      <c r="R2" s="3">
-        <v>0</v>
-      </c>
-      <c r="S2" s="3">
+      <c r="K2" s="4">
+        <v>0.155080443958291</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0.155080443958291</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0.155080443958291</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0.155080443958291</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0.0695173362502559</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0.155145202020202</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
         <v>0</v>
       </c>
     </row>
@@ -1228,229 +1303,229 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <f>SUM($B2:B2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="4">
         <f>SUM($B2:C2)</f>
         <v>0.3087350715503</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <f>SUM($B2:D2)</f>
         <v>0.463102607325449</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <f>SUM($B2:E2)</f>
         <v>0.617470143100599</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="4">
         <f>SUM($B2:F2)</f>
         <v>0.771837678875749</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="4">
         <f>SUM($B2:G2)</f>
         <v>0.926205214650899</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="4">
         <f>SUM($B2:H2)</f>
         <v>1</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="4">
         <f>SUM($B2:I2)</f>
         <v>1.15508044395829</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="4">
         <f>SUM($B2:J2)</f>
         <v>1.31016088791658</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="4">
         <f>SUM($B2:K2)</f>
-        <v>1.31016088791658</v>
-      </c>
-      <c r="L3" s="3">
+        <v>1.46524133187487</v>
+      </c>
+      <c r="L3" s="4">
         <f>SUM($B2:L2)</f>
-        <v>1.31016088791658</v>
-      </c>
-      <c r="M3" s="3">
+        <v>1.62032177583316</v>
+      </c>
+      <c r="M3" s="4">
         <f>SUM($B2:M2)</f>
-        <v>1.31016088791658</v>
-      </c>
-      <c r="N3" s="3">
+        <v>1.77540221979145</v>
+      </c>
+      <c r="N3" s="4">
         <f>SUM($B2:N2)</f>
-        <v>1.31016088791658</v>
-      </c>
-      <c r="O3" s="3">
+        <v>1.93048266374974</v>
+      </c>
+      <c r="O3" s="4">
         <f>SUM($B2:O2)</f>
-        <v>1.31016088791658</v>
-      </c>
-      <c r="P3" s="3">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
         <f>SUM($B2:P2)</f>
-        <v>1.31016088791658</v>
-      </c>
-      <c r="Q3" s="3">
+        <v>2.1551452020202</v>
+      </c>
+      <c r="Q3" s="4">
         <f>SUM($B2:Q2)</f>
-        <v>1.31016088791658</v>
-      </c>
-      <c r="R3" s="3">
+        <v>2.1551452020202</v>
+      </c>
+      <c r="R3" s="4">
         <f>SUM($B2:R2)</f>
-        <v>1.31016088791658</v>
-      </c>
-      <c r="S3" s="3">
+        <v>2.1551452020202</v>
+      </c>
+      <c r="S3" s="4">
         <f>SUM($B2:S2)</f>
-        <v>1.31016088791658</v>
+        <v>2.1551452020202</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <f>AVERAGE($B2:B2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="4">
         <f>AVERAGE($B2:C2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="4">
         <f>AVERAGE($B2:D2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="4">
         <f>AVERAGE($B2:E2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="4">
         <f>AVERAGE($B2:F2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="4">
         <f>AVERAGE($B2:G2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="4">
         <f>AVERAGE($B2:H2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="4">
         <f>AVERAGE($B2:I2)</f>
         <v>0.144385055494786</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="4">
         <f>AVERAGE($B2:J2)</f>
         <v>0.145573431990731</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="4">
         <f>AVERAGE($B2:K2)</f>
-        <v>0.131016088791658</v>
-      </c>
-      <c r="L4" s="3">
+        <v>0.146524133187487</v>
+      </c>
+      <c r="L4" s="4">
         <f>AVERAGE($B2:L2)</f>
-        <v>0.119105535265144</v>
-      </c>
-      <c r="M4" s="3">
+        <v>0.147301979621197</v>
+      </c>
+      <c r="M4" s="4">
         <f>AVERAGE($B2:M2)</f>
-        <v>0.109180073993049</v>
-      </c>
-      <c r="N4" s="3">
+        <v>0.147950184982621</v>
+      </c>
+      <c r="N4" s="4">
         <f>AVERAGE($B2:N2)</f>
-        <v>0.100781606762814</v>
-      </c>
-      <c r="O4" s="3">
+        <v>0.148498666442288</v>
+      </c>
+      <c r="O4" s="4">
         <f>AVERAGE($B2:O2)</f>
-        <v>0.0935829205654702</v>
-      </c>
-      <c r="P4" s="3">
+        <v>0.142857142857143</v>
+      </c>
+      <c r="P4" s="4">
         <f>AVERAGE($B2:P2)</f>
-        <v>0.0873440591944388</v>
-      </c>
-      <c r="Q4" s="3">
+        <v>0.143676346801347</v>
+      </c>
+      <c r="Q4" s="4">
         <f>AVERAGE($B2:Q2)</f>
-        <v>0.0818850554947864</v>
-      </c>
-      <c r="R4" s="3">
+        <v>0.134696575126263</v>
+      </c>
+      <c r="R4" s="4">
         <f>AVERAGE($B2:R2)</f>
-        <v>0.0770682875245048</v>
-      </c>
-      <c r="S4" s="3">
+        <v>0.126773247177659</v>
+      </c>
+      <c r="S4" s="4">
         <f>AVERAGE($B2:S2)</f>
-        <v>0.0727867159953657</v>
+        <v>0.119730289001122</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="4">
         <f t="shared" ref="C5:S5" si="0">B5</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="4">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
@@ -1459,75 +1534,75 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <f t="shared" ref="B6:S6" si="1">B5-B2</f>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="4">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="4">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="4">
         <f t="shared" si="1"/>
         <v>0.080051368497053</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="4">
         <f t="shared" si="1"/>
         <v>-0.00123429011213669</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="4">
         <f t="shared" si="1"/>
         <v>-0.00123429011213669</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="4">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="L6" s="3">
+        <v>-0.00123429011213669</v>
+      </c>
+      <c r="L6" s="4">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="M6" s="3">
+        <v>-0.00123429011213669</v>
+      </c>
+      <c r="M6" s="4">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="N6" s="3">
+        <v>-0.00123429011213669</v>
+      </c>
+      <c r="N6" s="4">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="O6" s="3">
+        <v>-0.00123429011213669</v>
+      </c>
+      <c r="O6" s="4">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="P6" s="3">
+        <v>0.0843288175958981</v>
+      </c>
+      <c r="P6" s="4">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="Q6" s="3">
+        <v>-0.00129904817404802</v>
+      </c>
+      <c r="Q6" s="4">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="4">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6" s="4">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
@@ -1573,18 +1648,18 @@
       <c r="B10" s="1">
         <v>100</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="4">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D10" s="1">
         <v>50</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="4">
         <f>AVERAGE(F$10:F10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="4">
         <f t="shared" ref="F10:F20" si="2">G10/B10</f>
         <v>0</v>
       </c>
@@ -1606,18 +1681,18 @@
       <c r="B11" s="1">
         <v>50</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="4">
         <f>C10</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D11" s="1">
         <v>25</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="4">
         <f>AVERAGE(F$10:F11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1676,7 +1751,7 @@
       <c r="B15" s="1">
         <v>257</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="4">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -1684,11 +1759,11 @@
         <f t="shared" ref="D10:D20" si="4">ROUND(B15*C15,0)</f>
         <v>40</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="4">
         <f>AVERAGE(F$15:F15)</f>
         <v>0.066147859922179</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="4">
         <f t="shared" si="2"/>
         <v>0.066147859922179</v>
       </c>
@@ -1699,7 +1774,7 @@
       <c r="H15" s="1">
         <v>240</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="6">
         <f t="shared" ref="I15:I20" si="5">MIN($J$14*D15,J15)</f>
         <v>257</v>
       </c>
@@ -1714,7 +1789,7 @@
       <c r="B16" s="1">
         <v>390</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="4">
         <f t="shared" ref="C16:C20" si="6">C15</f>
         <v>0.153846153846154</v>
       </c>
@@ -1722,11 +1797,11 @@
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="4">
         <f>AVERAGE(F$15:F16)</f>
         <v>0.071535468422628</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="4">
         <f t="shared" si="2"/>
         <v>0.0769230769230769</v>
       </c>
@@ -1737,7 +1812,7 @@
       <c r="H16" s="1">
         <v>360</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="6">
         <f t="shared" si="5"/>
         <v>390</v>
       </c>
@@ -1752,7 +1827,7 @@
       <c r="B17" s="1">
         <v>484</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="4">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -1760,11 +1835,11 @@
         <f t="shared" si="4"/>
         <v>74</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="4">
         <f>AVERAGE(F$15:F17)</f>
         <v>0.0752385216481432</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="4">
         <f t="shared" si="2"/>
         <v>0.0826446280991736</v>
       </c>
@@ -1775,7 +1850,7 @@
       <c r="H17" s="1">
         <v>444</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="6">
         <f t="shared" si="5"/>
         <v>484</v>
       </c>
@@ -1790,7 +1865,7 @@
       <c r="B18" s="1">
         <v>240</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="4">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -1798,11 +1873,11 @@
         <f t="shared" si="4"/>
         <v>37</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="4">
         <f>AVERAGE(F$15:F18)</f>
         <v>0.0751788912361074</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="4">
         <f t="shared" si="2"/>
         <v>0.075</v>
       </c>
@@ -1813,7 +1888,7 @@
       <c r="H18" s="1">
         <v>222</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="6">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
@@ -1828,7 +1903,7 @@
       <c r="B19" s="1">
         <v>271</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="4">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -1836,11 +1911,11 @@
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="4">
         <f>AVERAGE(F$15:F19)</f>
         <v>0.0741652532102881</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="4">
         <f t="shared" si="2"/>
         <v>0.0701107011070111</v>
       </c>
@@ -1851,7 +1926,7 @@
       <c r="H19" s="1">
         <v>252</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="6">
         <f t="shared" si="5"/>
         <v>271</v>
       </c>
@@ -1866,7 +1941,7 @@
       <c r="B20" s="1">
         <v>278</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="4">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -1874,11 +1949,11 @@
         <f t="shared" si="4"/>
         <v>43</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="4">
         <f>AVERAGE(F$15:F20)</f>
         <v>0.073794785349101</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="4">
         <f t="shared" si="2"/>
         <v>0.0719424460431655</v>
       </c>
@@ -1889,7 +1964,7 @@
       <c r="H20" s="1">
         <v>258</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="6">
         <f t="shared" si="5"/>
         <v>278</v>
       </c>
@@ -1898,17 +1973,17 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="C21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+      <c r="C21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+      <c r="C22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
@@ -1939,7 +2014,7 @@
         <v>15</v>
       </c>
       <c r="J23" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1949,7 +2024,7 @@
       <c r="B24" s="1">
         <v>440</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="4">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -1957,27 +2032,27 @@
         <f t="shared" ref="D24:D28" si="7">ROUND(B24*C24,0)</f>
         <v>68</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="4">
         <f>AVERAGE(F$24:F24)</f>
-        <v>0.154545454545455</v>
-      </c>
-      <c r="F24" s="3">
+        <v>0.0727272727272727</v>
+      </c>
+      <c r="F24" s="4">
         <f t="shared" ref="F24:F28" si="8">G24/B24</f>
-        <v>0.154545454545455</v>
+        <v>0.0727272727272727</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" ref="G24:G28" si="9">I24-H24</f>
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="H24" s="1">
-        <v>136</v>
-      </c>
-      <c r="I24" s="5">
+        <v>408</v>
+      </c>
+      <c r="I24" s="6">
         <f t="shared" ref="I24:I28" si="10">MIN($J$23*D24,J24)</f>
-        <v>204</v>
+        <v>440</v>
       </c>
       <c r="J24" s="1">
-        <v>322</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1987,7 +2062,7 @@
       <c r="B25" s="1">
         <v>378</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="4">
         <f t="shared" ref="C25:C28" si="11">C24</f>
         <v>0.153846153846154</v>
       </c>
@@ -1995,27 +2070,27 @@
         <f t="shared" si="7"/>
         <v>58</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="4">
         <f>AVERAGE(F$24:F25)</f>
-        <v>0.0865319865319865</v>
-      </c>
-      <c r="F25" s="3">
+        <v>0.076046176046176</v>
+      </c>
+      <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>0.0185185185185185</v>
+        <v>0.0793650793650794</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="H25" s="1">
-        <v>116</v>
+        <v>348</v>
       </c>
       <c r="I25" s="6">
         <f t="shared" si="10"/>
-        <v>123</v>
+        <v>378</v>
       </c>
       <c r="J25" s="1">
-        <v>123</v>
+        <v>378</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2025,7 +2100,7 @@
       <c r="B26" s="1">
         <v>209</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="4">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -2033,27 +2108,27 @@
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="4">
         <f>AVERAGE(F$24:F26)</f>
-        <v>0.0895859176560931</v>
-      </c>
-      <c r="F26" s="3">
+        <v>0.0778106883370041</v>
+      </c>
+      <c r="F26" s="4">
         <f t="shared" si="8"/>
-        <v>0.0956937799043062</v>
+        <v>0.0813397129186603</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="9"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H26" s="1">
-        <v>64</v>
+        <v>192</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="10"/>
-        <v>84</v>
+        <v>209</v>
       </c>
       <c r="J26" s="1">
-        <v>84</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2063,7 +2138,7 @@
       <c r="B27" s="1">
         <v>62</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="4">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -2071,27 +2146,27 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="4">
         <f>AVERAGE(F$24:F27)</f>
-        <v>0.107512018887231</v>
-      </c>
-      <c r="F27" s="3">
+        <v>0.0664225323817854</v>
+      </c>
+      <c r="F27" s="4">
         <f t="shared" si="8"/>
-        <v>0.161290322580645</v>
+        <v>0.032258064516129</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
+        <v>60</v>
+      </c>
+      <c r="I27" s="6">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="J27" s="1">
-        <v>40</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2101,7 +2176,7 @@
       <c r="B28" s="1">
         <v>464</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="4">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -2109,41 +2184,38 @@
         <f t="shared" si="7"/>
         <v>71</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="4">
         <f>AVERAGE(F$24:F28)</f>
-        <v>0.0898889254546125</v>
-      </c>
-      <c r="F28" s="3">
+        <v>0.0695173362502559</v>
+      </c>
+      <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>0.0193965517241379</v>
+        <v>0.0818965517241379</v>
       </c>
       <c r="G28" s="1">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="H28" s="1">
-        <v>142</v>
+        <v>426</v>
       </c>
       <c r="I28" s="6">
         <f t="shared" si="10"/>
-        <v>151</v>
+        <v>464</v>
       </c>
       <c r="J28" s="1">
-        <v>151</v>
+        <v>464</v>
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="C29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+      <c r="C29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
@@ -2182,30 +2254,30 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>177</v>
-      </c>
-      <c r="C32" s="3">
-        <f>4/26</f>
+        <v>132</v>
+      </c>
+      <c r="C32" s="4">
+        <f t="shared" ref="C32:C35" si="12">4/26</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D32" s="1">
-        <f>ROUND(B32*C32,0)</f>
-        <v>27</v>
-      </c>
-      <c r="E32" s="3">
+        <f t="shared" ref="D32:D35" si="13">ROUND(B32*C32,0)</f>
+        <v>20</v>
+      </c>
+      <c r="E32" s="4">
         <f>AVERAGE(F$32:F32)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="3">
-        <f>G32/B32</f>
+      <c r="F32" s="4">
+        <f t="shared" ref="F32:F35" si="14">G32/B32</f>
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <f>I32-H32</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" ref="I32:I35" si="12">MIN($J$31*D32,J32)</f>
+        <f t="shared" ref="G32:G35" si="15">I32-H32</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="6">
+        <f t="shared" ref="I32:I35" si="16">MIN($J$31*D32,J32)</f>
         <v>0</v>
       </c>
       <c r="J32" s="1">
@@ -2217,34 +2289,34 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>212</v>
-      </c>
-      <c r="C33" s="3">
-        <f t="shared" ref="C33:C35" si="13">C32</f>
+        <v>30</v>
+      </c>
+      <c r="C33" s="4">
+        <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D33" s="1">
-        <f>ROUND(B33*C33,0)</f>
-        <v>33</v>
-      </c>
-      <c r="E33" s="3">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="E33" s="4">
         <f>AVERAGE(F$32:F33)</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="3">
-        <f>G33/B33</f>
-        <v>0</v>
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="F33" s="4">
+        <f t="shared" si="14"/>
+        <v>0.0666666666666667</v>
       </c>
       <c r="G33" s="1">
-        <f>I33-H33</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>2</v>
+      </c>
+      <c r="I33" s="6">
+        <f t="shared" si="16"/>
+        <v>2</v>
       </c>
       <c r="J33" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2252,34 +2324,34 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>100</v>
-      </c>
-      <c r="C34" s="3">
+        <v>395</v>
+      </c>
+      <c r="C34" s="4">
+        <f t="shared" si="12"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D34" s="1">
         <f t="shared" si="13"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="D34" s="1">
-        <f>ROUND(B34*C34,0)</f>
-        <v>15</v>
-      </c>
-      <c r="E34" s="3">
+        <v>61</v>
+      </c>
+      <c r="E34" s="4">
         <f>AVERAGE(F$32:F34)</f>
-        <v>0.05</v>
-      </c>
-      <c r="F34" s="3">
-        <f>G34/B34</f>
-        <v>0.15</v>
+        <v>0.0222222222222222</v>
+      </c>
+      <c r="F34" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
-        <f>I34-H34</f>
-        <v>15</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="12"/>
-        <v>15</v>
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="6">
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2287,45 +2359,303 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
+        <v>66</v>
+      </c>
+      <c r="C35" s="4">
+        <f t="shared" si="12"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D35" s="1">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="E35" s="4">
+        <f>AVERAGE(F$32:F35)</f>
+        <v>0.0166666666666667</v>
+      </c>
+      <c r="F35" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="6">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J38" s="1">
         <v>1</v>
       </c>
-      <c r="C35" s="3">
-        <f t="shared" si="13"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="D35" s="1">
-        <f>ROUND(B35*C35,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="3">
-        <f>AVERAGE(F$32:F35)</f>
-        <v>0.0375</v>
-      </c>
-      <c r="F35" s="3">
-        <f>G35/B35</f>
-        <v>0</v>
-      </c>
-      <c r="G35" s="1">
-        <f>I35-H35</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="C36" s="3"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="1">
+        <v>100</v>
+      </c>
+      <c r="C39" s="4">
+        <f t="shared" ref="C39:C41" si="17">4/26</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D39" s="1">
+        <f>ROUND(B39*C39,0)</f>
+        <v>15</v>
+      </c>
+      <c r="E39" s="4">
+        <f>AVERAGE(F$39:F39)</f>
+        <v>0.15</v>
+      </c>
+      <c r="F39" s="4">
+        <f>G39/B39</f>
+        <v>0.15</v>
+      </c>
+      <c r="G39" s="1">
+        <f>I39-H39</f>
+        <v>15</v>
+      </c>
+      <c r="I39" s="6">
+        <f>MIN($J$38*D39,J39)</f>
+        <v>15</v>
+      </c>
+      <c r="J39" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1">
+        <v>298</v>
+      </c>
+      <c r="C40" s="4">
+        <f t="shared" si="17"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D40" s="1">
+        <f>ROUND(B40*C40,0)</f>
+        <v>46</v>
+      </c>
+      <c r="E40" s="4">
+        <f>AVERAGE(F$39:F40)</f>
+        <v>0.075</v>
+      </c>
+      <c r="F40" s="4">
+        <f>G40/B40</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <f>I40-H40</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="1">
+        <v>99</v>
+      </c>
+      <c r="C41" s="4">
+        <f t="shared" si="17"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D41" s="1">
+        <f>ROUND(B41*C41,0)</f>
+        <v>15</v>
+      </c>
+      <c r="E41" s="4">
+        <f>AVERAGE(F$39:F41)</f>
+        <v>0.05</v>
+      </c>
+      <c r="F41" s="4">
+        <f>G41/B41</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <f>I41-H41</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J44" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="1">
+        <f>177+7+212</f>
+        <v>396</v>
+      </c>
+      <c r="C45" s="4">
+        <f>4/26</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D45" s="1">
+        <f>ROUND(B45*C45,0)</f>
+        <v>61</v>
+      </c>
+      <c r="E45" s="4">
+        <f>AVERAGE(F$45:F45)</f>
+        <v>0.0202020202020202</v>
+      </c>
+      <c r="F45" s="4">
+        <f>G45/B45</f>
+        <v>0.0202020202020202</v>
+      </c>
+      <c r="G45" s="1">
+        <f>I45-H45</f>
+        <v>8</v>
+      </c>
+      <c r="H45" s="1">
+        <v>61</v>
+      </c>
+      <c r="I45" s="7">
+        <f>MIN($J$44*D45,J45)</f>
+        <v>69</v>
+      </c>
+      <c r="J45" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="1">
+        <f>16+16</f>
+        <v>32</v>
+      </c>
+      <c r="C46" s="4">
+        <f>C45</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D46" s="1">
+        <f>ROUND(B46*C46,0)</f>
+        <v>5</v>
+      </c>
+      <c r="E46" s="4">
+        <f>AVERAGE(F$45:F46)</f>
+        <v>0.0882260101010101</v>
+      </c>
+      <c r="F46" s="4">
+        <f>G46/B46</f>
+        <v>0.15625</v>
+      </c>
+      <c r="G46" s="1">
+        <f>I46-H46</f>
+        <v>5</v>
+      </c>
+      <c r="H46" s="1">
+        <v>5</v>
+      </c>
+      <c r="I46" s="6">
+        <f>MIN($J$44*D46,J46)</f>
+        <v>10</v>
+      </c>
+      <c r="J46" s="1">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="K2:S2 A1:S1 A2 A3:S8 A9:D9 A10:C11 A12:D14 K9:S20 C15:D16 A16 A17:D20" formulaRange="1"/>
+    <ignoredError sqref="Q2:S2 A1:S1 A2 A3:S8 A9:D9 A10:C11 A12:D14 K9:S20 C15:D16 A16 A17:D20" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2333,109 +2663,147 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="10.7777777777778" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultColWidth="10.7777777777778" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="16384" width="10.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="1">
         <v>202</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="D2" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="1">
         <v>390</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="D3" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="1">
         <v>484</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="D4" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="1">
         <v>240</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="D5" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="1">
         <v>271</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="D6" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="1">
         <v>278</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="D7" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="D8" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>440</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="1">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>378</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="1">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>209</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B13" s="1">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>32</v>
       </c>
@@ -2443,28 +2811,110 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="1">
-        <v>0</v>
+    <row r="21" spans="1:6">
+      <c r="A21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="C23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="1">
+        <f>SUM(C24:E24)</f>
+        <v>70</v>
+      </c>
+      <c r="C24" s="1">
+        <v>50</v>
+      </c>
+      <c r="D24" s="1">
+        <v>7</v>
+      </c>
+      <c r="E24" s="1">
+        <v>13</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="1">
+        <f>SUM(C25:D25)</f>
+        <v>11</v>
+      </c>
+      <c r="C25" s="1">
+        <v>11</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="C26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -210,7 +210,7 @@
     <t>视频#</t>
   </si>
   <si>
-    <t>1-6</t>
+    <t>2-2</t>
   </si>
 </sst>
 </file>
@@ -2590,25 +2590,25 @@
       </c>
       <c r="E45" s="4">
         <f>AVERAGE(F$45:F45)</f>
-        <v>0.0202020202020202</v>
+        <v>0.0454545454545455</v>
       </c>
       <c r="F45" s="4">
         <f>G45/B45</f>
-        <v>0.0202020202020202</v>
+        <v>0.0454545454545455</v>
       </c>
       <c r="G45" s="1">
         <f>I45-H45</f>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H45" s="1">
         <v>61</v>
       </c>
       <c r="I45" s="7">
         <f>MIN($J$44*D45,J45)</f>
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J45" s="1">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="E46" s="4">
         <f>AVERAGE(F$45:F46)</f>
-        <v>0.0882260101010101</v>
+        <v>0.100852272727273</v>
       </c>
       <c r="F46" s="4">
         <f>G46/B46</f>
@@ -2879,16 +2879,16 @@
       </c>
       <c r="B24" s="1">
         <f>SUM(C24:E24)</f>
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C24" s="1">
         <v>50</v>
       </c>
       <c r="D24" s="1">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E24" s="1">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>60</v>

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="进度" sheetId="1" r:id="rId1"/>
@@ -210,7 +210,7 @@
     <t>视频#</t>
   </si>
   <si>
-    <t>2-2</t>
+    <t>2-8</t>
   </si>
 </sst>
 </file>
@@ -1287,10 +1287,10 @@
         <v>0.0695173362502559</v>
       </c>
       <c r="P2" s="4">
-        <v>0.155145202020202</v>
+        <v>0.154780052264808</v>
       </c>
       <c r="Q2" s="4">
-        <v>0</v>
+        <v>0.154780052264808</v>
       </c>
       <c r="R2" s="4">
         <v>0</v>
@@ -1361,19 +1361,19 @@
       </c>
       <c r="P3" s="4">
         <f>SUM($B2:P2)</f>
-        <v>2.1551452020202</v>
+        <v>2.15478005226481</v>
       </c>
       <c r="Q3" s="4">
         <f>SUM($B2:Q2)</f>
-        <v>2.1551452020202</v>
+        <v>2.30956010452962</v>
       </c>
       <c r="R3" s="4">
         <f>SUM($B2:R2)</f>
-        <v>2.1551452020202</v>
+        <v>2.30956010452962</v>
       </c>
       <c r="S3" s="4">
         <f>SUM($B2:S2)</f>
-        <v>2.1551452020202</v>
+        <v>2.30956010452962</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1438,19 +1438,19 @@
       </c>
       <c r="P4" s="4">
         <f>AVERAGE($B2:P2)</f>
-        <v>0.143676346801347</v>
+        <v>0.143652003484321</v>
       </c>
       <c r="Q4" s="4">
         <f>AVERAGE($B2:Q2)</f>
-        <v>0.134696575126263</v>
+        <v>0.144347506533101</v>
       </c>
       <c r="R4" s="4">
         <f>AVERAGE($B2:R2)</f>
-        <v>0.126773247177659</v>
+        <v>0.135856476737036</v>
       </c>
       <c r="S4" s="4">
         <f>AVERAGE($B2:S2)</f>
-        <v>0.119730289001122</v>
+        <v>0.12830889469609</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1592,11 +1592,11 @@
       </c>
       <c r="P6" s="4">
         <f t="shared" si="1"/>
-        <v>-0.00129904817404802</v>
+        <v>-0.00093389841865435</v>
       </c>
       <c r="Q6" s="4">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
+        <v>-0.00093389841865435</v>
       </c>
       <c r="R6" s="4">
         <f t="shared" si="1"/>
@@ -2569,7 +2569,7 @@
         <v>15</v>
       </c>
       <c r="J44" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2577,8 +2577,8 @@
         <v>40</v>
       </c>
       <c r="B45" s="1">
-        <f>177+7+212</f>
-        <v>396</v>
+        <f>52+23+212</f>
+        <v>287</v>
       </c>
       <c r="C45" s="4">
         <f>4/26</f>
@@ -2586,29 +2586,29 @@
       </c>
       <c r="D45" s="1">
         <f>ROUND(B45*C45,0)</f>
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E45" s="4">
         <f>AVERAGE(F$45:F45)</f>
-        <v>0.0454545454545455</v>
+        <v>0.0801393728222996</v>
       </c>
       <c r="F45" s="4">
         <f>G45/B45</f>
-        <v>0.0454545454545455</v>
+        <v>0.0801393728222996</v>
       </c>
       <c r="G45" s="1">
         <f>I45-H45</f>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H45" s="1">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="I45" s="7">
         <f>MIN($J$44*D45,J45)</f>
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="J45" s="1">
-        <v>79</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2629,22 +2629,22 @@
       </c>
       <c r="E46" s="4">
         <f>AVERAGE(F$45:F46)</f>
-        <v>0.100852272727273</v>
+        <v>0.0556946864111498</v>
       </c>
       <c r="F46" s="4">
         <f>G46/B46</f>
-        <v>0.15625</v>
+        <v>0.03125</v>
       </c>
       <c r="G46" s="1">
         <f>I46-H46</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H46" s="1">
-        <v>5</v>
-      </c>
-      <c r="I46" s="6">
+        <v>10</v>
+      </c>
+      <c r="I46" s="7">
         <f>MIN($J$44*D46,J46)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J46" s="1">
         <v>11</v>
@@ -2655,7 +2655,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="Q2:S2 A1:S1 A2 A3:S8 A9:D9 A10:C11 A12:D14 K9:S20 C15:D16 A16 A17:D20" formulaRange="1"/>
+    <ignoredError sqref="R2:S2 A1:S1 A2 A3:S8 A9:D9 A10:C11 A12:D14 K9:S20 C15:D16 A16 A17:D20" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2879,16 +2879,16 @@
       </c>
       <c r="B24" s="1">
         <f>SUM(C24:E24)</f>
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="C24" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D24" s="1">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E24" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>60</v>

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="进度" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="71">
   <si>
     <t>日期</t>
   </si>
@@ -168,12 +168,27 @@
     <t>LMS</t>
   </si>
   <si>
+    <t>A review of visual perception technology for intelligent fruit harvesting robots</t>
+  </si>
+  <si>
     <t>CDCGAN</t>
   </si>
   <si>
+    <t>AI-empowered Channel Estimation for Block-based Active IRS-enhanced Hybrid-field IoT Network</t>
+  </si>
+  <si>
     <t>LabVIEW</t>
   </si>
   <si>
+    <t>GLN-LRF global learning network based on large receptive fields for hyperspectral image classification</t>
+  </si>
+  <si>
+    <t>LCD Panel</t>
+  </si>
+  <si>
+    <t>GPI-Net Gestalt-Guided Parallel Interaction Network via Orthogonal Geometric Consistency for Robust Point Cloud Registration</t>
+  </si>
+  <si>
     <t>OpenCog</t>
   </si>
   <si>
@@ -193,6 +208,21 @@
   </si>
   <si>
     <t>BioInfo</t>
+  </si>
+  <si>
+    <t>SigInt</t>
+  </si>
+  <si>
+    <t>IC Layout</t>
+  </si>
+  <si>
+    <t>SoftTST</t>
+  </si>
+  <si>
+    <t>Godot2D</t>
+  </si>
+  <si>
+    <t>OpenGL</t>
   </si>
   <si>
     <t>三论概述</t>
@@ -839,12 +869,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1185,58 +1218,58 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3">
+      <c r="B1" s="4">
         <v>46081</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="4">
         <v>46082</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="4">
         <v>46083</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="4">
         <v>46084</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="4">
         <v>46085</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="4">
         <v>46086</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="4">
         <v>46087</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="4">
         <v>46088</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="4">
         <v>46089</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="4">
         <v>46090</v>
       </c>
-      <c r="L1" s="3">
+      <c r="L1" s="4">
         <v>46091</v>
       </c>
-      <c r="M1" s="3">
+      <c r="M1" s="4">
         <v>46092</v>
       </c>
-      <c r="N1" s="3">
+      <c r="N1" s="4">
         <v>46093</v>
       </c>
-      <c r="O1" s="3">
+      <c r="O1" s="4">
         <v>46094</v>
       </c>
-      <c r="P1" s="3">
+      <c r="P1" s="4">
         <v>46095</v>
       </c>
-      <c r="Q1" s="3">
+      <c r="Q1" s="4">
         <v>46096</v>
       </c>
-      <c r="R1" s="3">
+      <c r="R1" s="4">
         <v>46097</v>
       </c>
-      <c r="S1" s="3">
+      <c r="S1" s="4">
         <v>46098</v>
       </c>
     </row>
@@ -1244,58 +1277,58 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="5">
         <v>0.15436753577515</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>0.15436753577515</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="5">
         <v>0.15436753577515</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="5">
         <v>0.15436753577515</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="5">
         <v>0.15436753577515</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <v>0.15436753577515</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="5">
         <v>0.073794785349101</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="6">
         <v>0.155080443958291</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="6">
         <v>0.155080443958291</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="5">
         <v>0.155080443958291</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="5">
         <v>0.155080443958291</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="5">
         <v>0.155080443958291</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="5">
         <v>0.155080443958291</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="5">
         <v>0.0695173362502559</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="5">
         <v>0.154780052264808</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="5">
         <v>0.154780052264808</v>
       </c>
-      <c r="R2" s="4">
-        <v>0</v>
-      </c>
-      <c r="S2" s="4">
+      <c r="R2" s="5">
+        <v>0.154780052264808</v>
+      </c>
+      <c r="S2" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1303,229 +1336,229 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="5">
         <f>SUM($B2:B2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <f>SUM($B2:C2)</f>
         <v>0.3087350715503</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="5">
         <f>SUM($B2:D2)</f>
         <v>0.463102607325449</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="5">
         <f>SUM($B2:E2)</f>
         <v>0.617470143100599</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="5">
         <f>SUM($B2:F2)</f>
         <v>0.771837678875749</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="5">
         <f>SUM($B2:G2)</f>
         <v>0.926205214650899</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="5">
         <f>SUM($B2:H2)</f>
         <v>1</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="5">
         <f>SUM($B2:I2)</f>
         <v>1.15508044395829</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="5">
         <f>SUM($B2:J2)</f>
         <v>1.31016088791658</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="5">
         <f>SUM($B2:K2)</f>
         <v>1.46524133187487</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="5">
         <f>SUM($B2:L2)</f>
         <v>1.62032177583316</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="5">
         <f>SUM($B2:M2)</f>
         <v>1.77540221979145</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3" s="5">
         <f>SUM($B2:N2)</f>
         <v>1.93048266374974</v>
       </c>
-      <c r="O3" s="4">
+      <c r="O3" s="5">
         <f>SUM($B2:O2)</f>
         <v>2</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="5">
         <f>SUM($B2:P2)</f>
         <v>2.15478005226481</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="Q3" s="5">
         <f>SUM($B2:Q2)</f>
         <v>2.30956010452962</v>
       </c>
-      <c r="R3" s="4">
+      <c r="R3" s="5">
         <f>SUM($B2:R2)</f>
-        <v>2.30956010452962</v>
-      </c>
-      <c r="S3" s="4">
+        <v>2.46434015679443</v>
+      </c>
+      <c r="S3" s="5">
         <f>SUM($B2:S2)</f>
-        <v>2.30956010452962</v>
+        <v>2.46434015679443</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5">
         <f>AVERAGE($B2:B2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <f>AVERAGE($B2:C2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <f>AVERAGE($B2:D2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <f>AVERAGE($B2:E2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="5">
         <f>AVERAGE($B2:F2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <f>AVERAGE($B2:G2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="5">
         <f>AVERAGE($B2:H2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="5">
         <f>AVERAGE($B2:I2)</f>
         <v>0.144385055494786</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <f>AVERAGE($B2:J2)</f>
         <v>0.145573431990731</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="5">
         <f>AVERAGE($B2:K2)</f>
         <v>0.146524133187487</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="5">
         <f>AVERAGE($B2:L2)</f>
         <v>0.147301979621197</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="5">
         <f>AVERAGE($B2:M2)</f>
         <v>0.147950184982621</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="5">
         <f>AVERAGE($B2:N2)</f>
         <v>0.148498666442288</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="5">
         <f>AVERAGE($B2:O2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="P4" s="4">
+      <c r="P4" s="5">
         <f>AVERAGE($B2:P2)</f>
         <v>0.143652003484321</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="Q4" s="5">
         <f>AVERAGE($B2:Q2)</f>
         <v>0.144347506533101</v>
       </c>
-      <c r="R4" s="4">
+      <c r="R4" s="5">
         <f>AVERAGE($B2:R2)</f>
-        <v>0.135856476737036</v>
-      </c>
-      <c r="S4" s="4">
+        <v>0.14496118569379</v>
+      </c>
+      <c r="S4" s="5">
         <f>AVERAGE($B2:S2)</f>
-        <v>0.12830889469609</v>
+        <v>0.136907786488579</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <f t="shared" ref="C5:S5" si="0">B5</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="O5" s="4">
+      <c r="O5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="Q5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="R5" s="4">
+      <c r="R5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="S5" s="4">
+      <c r="S5" s="5">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
@@ -1534,75 +1567,75 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="5">
         <f t="shared" ref="B6:S6" si="1">B5-B2</f>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="5">
         <f t="shared" si="1"/>
         <v>0.080051368497053</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="5">
         <f t="shared" si="1"/>
         <v>-0.00123429011213669</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="5">
         <f t="shared" si="1"/>
         <v>-0.00123429011213669</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="5">
         <f t="shared" si="1"/>
         <v>-0.00123429011213669</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="5">
         <f t="shared" si="1"/>
         <v>-0.00123429011213669</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="5">
         <f t="shared" si="1"/>
         <v>-0.00123429011213669</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6" s="5">
         <f t="shared" si="1"/>
         <v>-0.00123429011213669</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="5">
         <f t="shared" si="1"/>
         <v>0.0843288175958981</v>
       </c>
-      <c r="P6" s="4">
+      <c r="P6" s="5">
         <f t="shared" si="1"/>
         <v>-0.00093389841865435</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="Q6" s="5">
         <f t="shared" si="1"/>
         <v>-0.00093389841865435</v>
       </c>
-      <c r="R6" s="4">
+      <c r="R6" s="5">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="S6" s="4">
+        <v>-0.00093389841865435</v>
+      </c>
+      <c r="S6" s="5">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
@@ -1648,18 +1681,18 @@
       <c r="B10" s="1">
         <v>100</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D10" s="1">
         <v>50</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <f>AVERAGE(F$10:F10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="5">
         <f t="shared" ref="F10:F20" si="2">G10/B10</f>
         <v>0</v>
       </c>
@@ -1681,18 +1714,18 @@
       <c r="B11" s="1">
         <v>50</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <f>C10</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D11" s="1">
         <v>25</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <f>AVERAGE(F$10:F11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1751,7 +1784,7 @@
       <c r="B15" s="1">
         <v>257</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -1759,11 +1792,11 @@
         <f t="shared" ref="D10:D20" si="4">ROUND(B15*C15,0)</f>
         <v>40</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="5">
         <f>AVERAGE(F$15:F15)</f>
         <v>0.066147859922179</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="5">
         <f t="shared" si="2"/>
         <v>0.066147859922179</v>
       </c>
@@ -1774,7 +1807,7 @@
       <c r="H15" s="1">
         <v>240</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="7">
         <f t="shared" ref="I15:I20" si="5">MIN($J$14*D15,J15)</f>
         <v>257</v>
       </c>
@@ -1789,7 +1822,7 @@
       <c r="B16" s="1">
         <v>390</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <f t="shared" ref="C16:C20" si="6">C15</f>
         <v>0.153846153846154</v>
       </c>
@@ -1797,11 +1830,11 @@
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <f>AVERAGE(F$15:F16)</f>
         <v>0.071535468422628</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="5">
         <f t="shared" si="2"/>
         <v>0.0769230769230769</v>
       </c>
@@ -1812,7 +1845,7 @@
       <c r="H16" s="1">
         <v>360</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="7">
         <f t="shared" si="5"/>
         <v>390</v>
       </c>
@@ -1827,7 +1860,7 @@
       <c r="B17" s="1">
         <v>484</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -1835,11 +1868,11 @@
         <f t="shared" si="4"/>
         <v>74</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="5">
         <f>AVERAGE(F$15:F17)</f>
         <v>0.0752385216481432</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="5">
         <f t="shared" si="2"/>
         <v>0.0826446280991736</v>
       </c>
@@ -1850,7 +1883,7 @@
       <c r="H17" s="1">
         <v>444</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="7">
         <f t="shared" si="5"/>
         <v>484</v>
       </c>
@@ -1865,7 +1898,7 @@
       <c r="B18" s="1">
         <v>240</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="5">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -1873,11 +1906,11 @@
         <f t="shared" si="4"/>
         <v>37</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="5">
         <f>AVERAGE(F$15:F18)</f>
         <v>0.0751788912361074</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="5">
         <f t="shared" si="2"/>
         <v>0.075</v>
       </c>
@@ -1888,7 +1921,7 @@
       <c r="H18" s="1">
         <v>222</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="7">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
@@ -1903,7 +1936,7 @@
       <c r="B19" s="1">
         <v>271</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -1911,11 +1944,11 @@
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="5">
         <f>AVERAGE(F$15:F19)</f>
         <v>0.0741652532102881</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="5">
         <f t="shared" si="2"/>
         <v>0.0701107011070111</v>
       </c>
@@ -1926,7 +1959,7 @@
       <c r="H19" s="1">
         <v>252</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="7">
         <f t="shared" si="5"/>
         <v>271</v>
       </c>
@@ -1941,7 +1974,7 @@
       <c r="B20" s="1">
         <v>278</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -1949,11 +1982,11 @@
         <f t="shared" si="4"/>
         <v>43</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="5">
         <f>AVERAGE(F$15:F20)</f>
         <v>0.073794785349101</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="5">
         <f t="shared" si="2"/>
         <v>0.0719424460431655</v>
       </c>
@@ -1964,7 +1997,7 @@
       <c r="H20" s="1">
         <v>258</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="7">
         <f t="shared" si="5"/>
         <v>278</v>
       </c>
@@ -1973,17 +2006,17 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="C21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
+      <c r="C21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+      <c r="C22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
@@ -2024,7 +2057,7 @@
       <c r="B24" s="1">
         <v>440</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="5">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -2032,11 +2065,11 @@
         <f t="shared" ref="D24:D28" si="7">ROUND(B24*C24,0)</f>
         <v>68</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="5">
         <f>AVERAGE(F$24:F24)</f>
         <v>0.0727272727272727</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="5">
         <f t="shared" ref="F24:F28" si="8">G24/B24</f>
         <v>0.0727272727272727</v>
       </c>
@@ -2047,7 +2080,7 @@
       <c r="H24" s="1">
         <v>408</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="7">
         <f t="shared" ref="I24:I28" si="10">MIN($J$23*D24,J24)</f>
         <v>440</v>
       </c>
@@ -2062,7 +2095,7 @@
       <c r="B25" s="1">
         <v>378</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="5">
         <f t="shared" ref="C25:C28" si="11">C24</f>
         <v>0.153846153846154</v>
       </c>
@@ -2070,11 +2103,11 @@
         <f t="shared" si="7"/>
         <v>58</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="5">
         <f>AVERAGE(F$24:F25)</f>
         <v>0.076046176046176</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="5">
         <f t="shared" si="8"/>
         <v>0.0793650793650794</v>
       </c>
@@ -2085,7 +2118,7 @@
       <c r="H25" s="1">
         <v>348</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="7">
         <f t="shared" si="10"/>
         <v>378</v>
       </c>
@@ -2100,7 +2133,7 @@
       <c r="B26" s="1">
         <v>209</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="5">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -2108,11 +2141,11 @@
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="5">
         <f>AVERAGE(F$24:F26)</f>
         <v>0.0778106883370041</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="5">
         <f t="shared" si="8"/>
         <v>0.0813397129186603</v>
       </c>
@@ -2123,7 +2156,7 @@
       <c r="H26" s="1">
         <v>192</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="7">
         <f t="shared" si="10"/>
         <v>209</v>
       </c>
@@ -2138,7 +2171,7 @@
       <c r="B27" s="1">
         <v>62</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="5">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -2146,11 +2179,11 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="5">
         <f>AVERAGE(F$24:F27)</f>
         <v>0.0664225323817854</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="5">
         <f t="shared" si="8"/>
         <v>0.032258064516129</v>
       </c>
@@ -2161,7 +2194,7 @@
       <c r="H27" s="1">
         <v>60</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="7">
         <f t="shared" si="10"/>
         <v>62</v>
       </c>
@@ -2176,7 +2209,7 @@
       <c r="B28" s="1">
         <v>464</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="5">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -2184,11 +2217,11 @@
         <f t="shared" si="7"/>
         <v>71</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="5">
         <f>AVERAGE(F$24:F28)</f>
         <v>0.0695173362502559</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="5">
         <f t="shared" si="8"/>
         <v>0.0818965517241379</v>
       </c>
@@ -2199,7 +2232,7 @@
       <c r="H28" s="1">
         <v>426</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I28" s="7">
         <f t="shared" si="10"/>
         <v>464</v>
       </c>
@@ -2208,9 +2241,9 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="C29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+      <c r="C29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
@@ -2256,7 +2289,7 @@
       <c r="B32" s="1">
         <v>132</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="5">
         <f t="shared" ref="C32:C35" si="12">4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -2264,11 +2297,11 @@
         <f t="shared" ref="D32:D35" si="13">ROUND(B32*C32,0)</f>
         <v>20</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="5">
         <f>AVERAGE(F$32:F32)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="5">
         <f t="shared" ref="F32:F35" si="14">G32/B32</f>
         <v>0</v>
       </c>
@@ -2276,7 +2309,7 @@
         <f t="shared" ref="G32:G35" si="15">I32-H32</f>
         <v>0</v>
       </c>
-      <c r="I32" s="6">
+      <c r="I32" s="7">
         <f t="shared" ref="I32:I35" si="16">MIN($J$31*D32,J32)</f>
         <v>0</v>
       </c>
@@ -2291,7 +2324,7 @@
       <c r="B33" s="1">
         <v>30</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="5">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
@@ -2299,11 +2332,11 @@
         <f t="shared" si="13"/>
         <v>5</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="5">
         <f>AVERAGE(F$32:F33)</f>
         <v>0.0333333333333333</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="5">
         <f t="shared" si="14"/>
         <v>0.0666666666666667</v>
       </c>
@@ -2311,7 +2344,7 @@
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="I33" s="6">
+      <c r="I33" s="7">
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
@@ -2326,7 +2359,7 @@
       <c r="B34" s="1">
         <v>395</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="5">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
@@ -2334,11 +2367,11 @@
         <f t="shared" si="13"/>
         <v>61</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="5">
         <f>AVERAGE(F$32:F34)</f>
         <v>0.0222222222222222</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="5">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -2346,7 +2379,7 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="7">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -2361,7 +2394,7 @@
       <c r="B35" s="1">
         <v>66</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="5">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
@@ -2369,11 +2402,11 @@
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="5">
         <f>AVERAGE(F$32:F35)</f>
         <v>0.0166666666666667</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="5">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -2381,7 +2414,7 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I35" s="6">
+      <c r="I35" s="7">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -2393,9 +2426,9 @@
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
+      <c r="C37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="1" t="s">
@@ -2436,7 +2469,7 @@
       <c r="B39" s="1">
         <v>100</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="5">
         <f t="shared" ref="C39:C41" si="17">4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -2444,11 +2477,11 @@
         <f>ROUND(B39*C39,0)</f>
         <v>15</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="5">
         <f>AVERAGE(F$39:F39)</f>
         <v>0.15</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="5">
         <f>G39/B39</f>
         <v>0.15</v>
       </c>
@@ -2456,7 +2489,7 @@
         <f>I39-H39</f>
         <v>15</v>
       </c>
-      <c r="I39" s="6">
+      <c r="I39" s="7">
         <f>MIN($J$38*D39,J39)</f>
         <v>15</v>
       </c>
@@ -2471,7 +2504,7 @@
       <c r="B40" s="1">
         <v>298</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="5">
         <f t="shared" si="17"/>
         <v>0.153846153846154</v>
       </c>
@@ -2479,11 +2512,11 @@
         <f>ROUND(B40*C40,0)</f>
         <v>46</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="5">
         <f>AVERAGE(F$39:F40)</f>
         <v>0.075</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="5">
         <f>G40/B40</f>
         <v>0</v>
       </c>
@@ -2505,7 +2538,7 @@
       <c r="B41" s="1">
         <v>99</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="5">
         <f t="shared" si="17"/>
         <v>0.153846153846154</v>
       </c>
@@ -2513,11 +2546,11 @@
         <f>ROUND(B41*C41,0)</f>
         <v>15</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="5">
         <f>AVERAGE(F$39:F41)</f>
         <v>0.05</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="5">
         <f>G41/B41</f>
         <v>0</v>
       </c>
@@ -2536,9 +2569,9 @@
       <c r="A43" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
+      <c r="C43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
@@ -2569,7 +2602,7 @@
         <v>15</v>
       </c>
       <c r="J44" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2580,7 +2613,7 @@
         <f>52+23+212</f>
         <v>287</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="5">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -2588,27 +2621,27 @@
         <f>ROUND(B45*C45,0)</f>
         <v>44</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E45" s="5">
         <f>AVERAGE(F$45:F45)</f>
-        <v>0.0801393728222996</v>
-      </c>
-      <c r="F45" s="4">
+        <v>0.0348432055749129</v>
+      </c>
+      <c r="F45" s="5">
         <f>G45/B45</f>
-        <v>0.0801393728222996</v>
+        <v>0.0348432055749129</v>
       </c>
       <c r="G45" s="1">
         <f>I45-H45</f>
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H45" s="1">
-        <v>88</v>
-      </c>
-      <c r="I45" s="7">
+        <v>132</v>
+      </c>
+      <c r="I45" s="8">
         <f>MIN($J$44*D45,J45)</f>
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="J45" s="1">
-        <v>111</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2616,10 +2649,10 @@
         <v>41</v>
       </c>
       <c r="B46" s="1">
-        <f>16+16</f>
-        <v>32</v>
-      </c>
-      <c r="C46" s="4">
+        <f>16+15</f>
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
         <f>C45</f>
         <v>0.153846153846154</v>
       </c>
@@ -2627,27 +2660,27 @@
         <f>ROUND(B46*C46,0)</f>
         <v>5</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E46" s="5">
         <f>AVERAGE(F$45:F46)</f>
-        <v>0.0556946864111498</v>
-      </c>
-      <c r="F46" s="4">
+        <v>0.098066764077779</v>
+      </c>
+      <c r="F46" s="5">
         <f>G46/B46</f>
-        <v>0.03125</v>
+        <v>0.161290322580645</v>
       </c>
       <c r="G46" s="1">
         <f>I46-H46</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H46" s="1">
-        <v>10</v>
-      </c>
-      <c r="I46" s="7">
+        <v>15</v>
+      </c>
+      <c r="I46" s="8">
         <f>MIN($J$44*D46,J46)</f>
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J46" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2655,7 +2688,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="R2:S2 A1:S1 A2 A3:S8 A9:D9 A10:C11 A12:D14 K9:S20 C15:D16 A16 A17:D20" formulaRange="1"/>
+    <ignoredError sqref="A17:D20 A16 C15:D16 K9:S20 A12:D14 A10:C11 A9:D9 A3:S8 A2 A1:S1 S2" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2693,6 +2726,9 @@
       <c r="D2" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="E2" s="2" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
@@ -2702,7 +2738,10 @@
         <v>390</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2713,7 +2752,10 @@
         <v>484</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2724,7 +2766,10 @@
         <v>240</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2735,8 +2780,9 @@
         <v>271</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
@@ -2746,13 +2792,15 @@
         <v>278</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
       <c r="D8" s="1" t="s">
-        <v>51</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
@@ -2762,8 +2810,9 @@
         <v>440</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
@@ -2773,8 +2822,9 @@
         <v>378</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>53</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
@@ -2784,8 +2834,9 @@
         <v>209</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
@@ -2794,6 +2845,10 @@
       <c r="B12" s="1">
         <v>62</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
@@ -2802,6 +2857,16 @@
       <c r="B13" s="1">
         <v>464</v>
       </c>
+      <c r="D13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="D14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
@@ -2810,6 +2875,10 @@
       <c r="B15" s="1">
         <v>0</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
@@ -2818,6 +2887,10 @@
       <c r="B16" s="1">
         <v>2</v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
@@ -2826,10 +2899,13 @@
       <c r="B17" s="1">
         <v>0</v>
       </c>
+      <c r="D17" s="1" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B18" s="1">
         <v>0</v>
@@ -2861,16 +2937,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="C23" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2879,10 +2955,10 @@
       </c>
       <c r="B24" s="1">
         <f>SUM(C24:E24)</f>
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C24" s="1">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="D24" s="1">
         <v>45</v>
@@ -2890,8 +2966,8 @@
       <c r="E24" s="1">
         <v>23</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>60</v>
+      <c r="F24" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2900,13 +2976,13 @@
       </c>
       <c r="B25" s="1">
         <f>SUM(C25:D25)</f>
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C25" s="1">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:6">

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="72">
   <si>
     <t>日期</t>
   </si>
@@ -190,6 +190,9 @@
   </si>
   <si>
     <t>OpenCog</t>
+  </si>
+  <si>
+    <t>Multiple attribute group decision making based on nucleolus weight and continuous optimal distance measure</t>
   </si>
   <si>
     <t>OpenNARS</t>
@@ -2675,12 +2678,12 @@
       <c r="H46" s="1">
         <v>15</v>
       </c>
-      <c r="I46" s="8">
+      <c r="I46" s="7">
         <f>MIN($J$44*D46,J46)</f>
         <v>20</v>
       </c>
       <c r="J46" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -2782,7 +2785,9 @@
       <c r="D6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
@@ -2792,13 +2797,13 @@
         <v>278</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
       <c r="D8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -2810,7 +2815,7 @@
         <v>440</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -2822,7 +2827,7 @@
         <v>378</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -2834,7 +2839,7 @@
         <v>209</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -2846,7 +2851,7 @@
         <v>62</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -2858,13 +2863,13 @@
         <v>464</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5">
       <c r="D14" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -2876,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -2888,7 +2893,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -2900,12 +2905,12 @@
         <v>0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="1">
         <v>0</v>
@@ -2937,16 +2942,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="C23" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2967,7 +2972,7 @@
         <v>23</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2976,13 +2981,13 @@
       </c>
       <c r="B25" s="1">
         <f>SUM(C25:D25)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C25" s="1">
         <v>16</v>
       </c>
       <c r="D25" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6">

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -243,7 +243,7 @@
     <t>视频#</t>
   </si>
   <si>
-    <t>2-8</t>
+    <t>3-8</t>
   </si>
 </sst>
 </file>
@@ -1211,13 +1211,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="15.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1275,8 +1275,38 @@
       <c r="S1" s="4">
         <v>46098</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" s="4">
+        <v>46099</v>
+      </c>
+      <c r="U1" s="4">
+        <v>46100</v>
+      </c>
+      <c r="V1" s="4">
+        <v>46101</v>
+      </c>
+      <c r="W1" s="4">
+        <v>46102</v>
+      </c>
+      <c r="X1" s="4">
+        <v>46103</v>
+      </c>
+      <c r="Y1" s="4">
+        <v>46104</v>
+      </c>
+      <c r="Z1" s="4">
+        <v>46105</v>
+      </c>
+      <c r="AA1" s="4">
+        <v>46106</v>
+      </c>
+      <c r="AB1" s="4">
+        <v>46107</v>
+      </c>
+      <c r="AC1" s="4">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1323,19 +1353,49 @@
         <v>0.0695173362502559</v>
       </c>
       <c r="P2" s="5">
-        <v>0.154780052264808</v>
+        <v>0.156916347731001</v>
       </c>
       <c r="Q2" s="5">
-        <v>0.154780052264808</v>
+        <v>0.156916347731001</v>
       </c>
       <c r="R2" s="5">
-        <v>0.154780052264808</v>
+        <v>0.156916347731001</v>
       </c>
       <c r="S2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
+        <v>0.156916347731001</v>
+      </c>
+      <c r="T2" s="5">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5">
+        <v>0</v>
+      </c>
+      <c r="W2" s="5">
+        <v>0</v>
+      </c>
+      <c r="X2" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1397,22 +1457,62 @@
       </c>
       <c r="P3" s="5">
         <f>SUM($B2:P2)</f>
-        <v>2.15478005226481</v>
+        <v>2.156916347731</v>
       </c>
       <c r="Q3" s="5">
         <f>SUM($B2:Q2)</f>
-        <v>2.30956010452962</v>
+        <v>2.313832695462</v>
       </c>
       <c r="R3" s="5">
         <f>SUM($B2:R2)</f>
-        <v>2.46434015679443</v>
+        <v>2.470749043193</v>
       </c>
       <c r="S3" s="5">
         <f>SUM($B2:S2)</f>
-        <v>2.46434015679443</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19">
+        <v>2.627665390924</v>
+      </c>
+      <c r="T3" s="5">
+        <f>SUM($B2:T2)</f>
+        <v>2.627665390924</v>
+      </c>
+      <c r="U3" s="5">
+        <f>SUM($B2:U2)</f>
+        <v>2.627665390924</v>
+      </c>
+      <c r="V3" s="5">
+        <f>SUM($B2:V2)</f>
+        <v>2.627665390924</v>
+      </c>
+      <c r="W3" s="5">
+        <f>SUM($B2:W2)</f>
+        <v>2.627665390924</v>
+      </c>
+      <c r="X3" s="5">
+        <f>SUM($B2:X2)</f>
+        <v>2.627665390924</v>
+      </c>
+      <c r="Y3" s="5">
+        <f>SUM($B2:Y2)</f>
+        <v>2.627665390924</v>
+      </c>
+      <c r="Z3" s="5">
+        <f>SUM($B2:Z2)</f>
+        <v>2.627665390924</v>
+      </c>
+      <c r="AA3" s="5">
+        <f>SUM($B2:AA2)</f>
+        <v>2.627665390924</v>
+      </c>
+      <c r="AB3" s="5">
+        <f>SUM($B2:AB2)</f>
+        <v>2.627665390924</v>
+      </c>
+      <c r="AC3" s="5">
+        <f>SUM($B2:AC2)</f>
+        <v>2.627665390924</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1474,22 +1574,62 @@
       </c>
       <c r="P4" s="5">
         <f>AVERAGE($B2:P2)</f>
-        <v>0.143652003484321</v>
+        <v>0.143794423182067</v>
       </c>
       <c r="Q4" s="5">
         <f>AVERAGE($B2:Q2)</f>
-        <v>0.144347506533101</v>
+        <v>0.144614543466375</v>
       </c>
       <c r="R4" s="5">
         <f>AVERAGE($B2:R2)</f>
-        <v>0.14496118569379</v>
+        <v>0.145338179011353</v>
       </c>
       <c r="S4" s="5">
         <f>AVERAGE($B2:S2)</f>
-        <v>0.136907786488579</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
+        <v>0.145981410606889</v>
+      </c>
+      <c r="T4" s="5">
+        <f>AVERAGE($B2:T2)</f>
+        <v>0.138298178469684</v>
+      </c>
+      <c r="U4" s="5">
+        <f>AVERAGE($B2:U2)</f>
+        <v>0.1313832695462</v>
+      </c>
+      <c r="V4" s="5">
+        <f>AVERAGE($B2:V2)</f>
+        <v>0.125126923377334</v>
+      </c>
+      <c r="W4" s="5">
+        <f>AVERAGE($B2:W2)</f>
+        <v>0.119439335951091</v>
+      </c>
+      <c r="X4" s="5">
+        <f>AVERAGE($B2:X2)</f>
+        <v>0.114246321344522</v>
+      </c>
+      <c r="Y4" s="5">
+        <f>AVERAGE($B2:Y2)</f>
+        <v>0.109486057955167</v>
+      </c>
+      <c r="Z4" s="5">
+        <f>AVERAGE($B2:Z2)</f>
+        <v>0.10510661563696</v>
+      </c>
+      <c r="AA4" s="5">
+        <f>AVERAGE($B2:AA2)</f>
+        <v>0.101064053497077</v>
+      </c>
+      <c r="AB4" s="5">
+        <f>AVERAGE($B2:AB2)</f>
+        <v>0.0973209404045928</v>
+      </c>
+      <c r="AC4" s="5">
+        <f>AVERAGE($B2:AC2)</f>
+        <v>0.0938451925330002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1565,8 +1705,48 @@
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="T5" s="5">
+        <f>S5</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="U5" s="5">
+        <f>T5</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="V5" s="5">
+        <f>U5</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="W5" s="5">
+        <f>V5</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="X5" s="5">
+        <f>W5</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="Y5" s="5">
+        <f>X5</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="Z5" s="5">
+        <f>Y5</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AA5" s="5">
+        <f>Z5</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AB5" s="5">
+        <f>AA5</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AC5" s="5">
+        <f>AB5</f>
+        <v>0.153846153846154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1600,27 +1780,27 @@
       </c>
       <c r="I6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.00123429011213669</v>
+        <v>-0.00123429011213699</v>
       </c>
       <c r="J6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.00123429011213669</v>
+        <v>-0.00123429011213699</v>
       </c>
       <c r="K6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.00123429011213669</v>
+        <v>-0.00123429011213699</v>
       </c>
       <c r="L6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.00123429011213669</v>
+        <v>-0.00123429011213699</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.00123429011213669</v>
+        <v>-0.00123429011213699</v>
       </c>
       <c r="N6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.00123429011213669</v>
+        <v>-0.00123429011213699</v>
       </c>
       <c r="O6" s="5">
         <f t="shared" si="1"/>
@@ -1628,27 +1808,67 @@
       </c>
       <c r="P6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.00093389841865435</v>
+        <v>-0.00307019388484656</v>
       </c>
       <c r="Q6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.00093389841865435</v>
+        <v>-0.00307019388484656</v>
       </c>
       <c r="R6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.00093389841865435</v>
+        <v>-0.00307019388484656</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
+        <v>-0.00307019388484656</v>
+      </c>
+      <c r="T6" s="5">
+        <f>T5-T2</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="U6" s="5">
+        <f>U5-U2</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="V6" s="5">
+        <f>V5-V2</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="W6" s="5">
+        <f>W5-W2</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="X6" s="5">
+        <f>X5-X2</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="Y6" s="5">
+        <f>Y5-Y2</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="Z6" s="5">
+        <f>Z5-Z2</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AA6" s="5">
+        <f>AA5-AA2</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AB6" s="5">
+        <f>AB5-AB2</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AC6" s="5">
+        <f>AC5-AC2</f>
+        <v>0.153846153846154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:29">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -1677,7 +1897,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:29">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -1710,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:29">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -1743,12 +1963,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:29">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:29">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -1780,7 +2000,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:29">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -1818,7 +2038,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:29">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
@@ -2605,7 +2825,7 @@
         <v>15</v>
       </c>
       <c r="J44" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2613,8 +2833,8 @@
         <v>40</v>
       </c>
       <c r="B45" s="1">
-        <f>52+23+212</f>
-        <v>287</v>
+        <f>212+52+31</f>
+        <v>295</v>
       </c>
       <c r="C45" s="5">
         <f>4/26</f>
@@ -2622,29 +2842,29 @@
       </c>
       <c r="D45" s="1">
         <f>ROUND(B45*C45,0)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E45" s="5">
         <f>AVERAGE(F$45:F45)</f>
-        <v>0.0348432055749129</v>
+        <v>0.0135593220338983</v>
       </c>
       <c r="F45" s="5">
         <f>G45/B45</f>
-        <v>0.0348432055749129</v>
+        <v>0.0135593220338983</v>
       </c>
       <c r="G45" s="1">
         <f>I45-H45</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H45" s="1">
-        <v>132</v>
+        <v>180</v>
       </c>
       <c r="I45" s="8">
         <f>MIN($J$44*D45,J45)</f>
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="J45" s="1">
-        <v>142</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2665,22 +2885,22 @@
       </c>
       <c r="E46" s="5">
         <f>AVERAGE(F$45:F46)</f>
-        <v>0.098066764077779</v>
+        <v>0.0229086932750137</v>
       </c>
       <c r="F46" s="5">
         <f>G46/B46</f>
-        <v>0.161290322580645</v>
+        <v>0.032258064516129</v>
       </c>
       <c r="G46" s="1">
         <f>I46-H46</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H46" s="1">
-        <v>15</v>
-      </c>
-      <c r="I46" s="7">
+        <v>20</v>
+      </c>
+      <c r="I46" s="8">
         <f>MIN($J$44*D46,J46)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J46" s="1">
         <v>21</v>
@@ -2691,7 +2911,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A17:D20 A16 C15:D16 K9:S20 A12:D14 A10:C11 A9:D9 A3:S8 A2 A1:S1 S2" formulaRange="1"/>
+    <ignoredError sqref="A1:AC46" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2960,16 +3180,16 @@
       </c>
       <c r="B24" s="1">
         <f>SUM(C24:E24)</f>
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="C24" s="1">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="D24" s="1">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E24" s="1">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>71</v>

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="进度" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="77">
   <si>
     <t>日期</t>
   </si>
@@ -198,16 +198,31 @@
     <t>OpenNARS</t>
   </si>
   <si>
+    <t>Semantic Communication for Efficient Point Cloud Transmission</t>
+  </si>
+  <si>
     <t>YOLO</t>
   </si>
   <si>
+    <t>Discrete comprehensive learning particle swarm optimization algorithm with Metropolis acceptance criterion for traveling salesman problem</t>
+  </si>
+  <si>
     <t>FaceNet</t>
   </si>
   <si>
+    <t>Discrete pigeon-inspired optimization algorithm with Metropolis acceptance criterion for large-scale traveling salesman problem</t>
+  </si>
+  <si>
     <t>BCI</t>
   </si>
   <si>
+    <t>List-based Simulated Annealing Algorithm with Hybrid Greedy Repair and Optimization Operator for 0-1 Knapsack Problem</t>
+  </si>
+  <si>
     <t>MedImg</t>
+  </si>
+  <si>
+    <t>Noising methods with hybrid greedy repair operator for 0–1 knapsack problem</t>
   </si>
   <si>
     <t>BioInfo</t>
@@ -2885,25 +2900,25 @@
       </c>
       <c r="E46" s="5">
         <f>AVERAGE(F$45:F46)</f>
-        <v>0.0229086932750137</v>
+        <v>0.0874248223072717</v>
       </c>
       <c r="F46" s="5">
         <f>G46/B46</f>
-        <v>0.032258064516129</v>
+        <v>0.161290322580645</v>
       </c>
       <c r="G46" s="1">
         <f>I46-H46</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H46" s="1">
         <v>20</v>
       </c>
-      <c r="I46" s="8">
+      <c r="I46" s="7">
         <f>MIN($J$44*D46,J46)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J46" s="1">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2911,7 +2926,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AC46" formulaRange="1"/>
+    <ignoredError sqref="A1:AC45 A46:I46 K46:AC46" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3019,13 +3034,17 @@
       <c r="D7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="D8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
@@ -3035,9 +3054,11 @@
         <v>440</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
@@ -3047,9 +3068,11 @@
         <v>378</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
@@ -3059,9 +3082,11 @@
         <v>209</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
@@ -3071,7 +3096,7 @@
         <v>62</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -3083,13 +3108,13 @@
         <v>464</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5">
       <c r="D14" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -3101,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -3113,7 +3138,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -3125,12 +3150,12 @@
         <v>0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B18" s="1">
         <v>0</v>
@@ -3162,16 +3187,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="C23" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -3192,7 +3217,7 @@
         <v>31</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -3201,13 +3226,13 @@
       </c>
       <c r="B25" s="1">
         <f>SUM(C25:D25)</f>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C25" s="1">
         <v>16</v>
       </c>
       <c r="D25" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:6">

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="进度" sheetId="1" r:id="rId1"/>
@@ -1380,7 +1380,7 @@
         <v>0.156916347731001</v>
       </c>
       <c r="T2" s="5">
-        <v>0</v>
+        <v>0.156916347731001</v>
       </c>
       <c r="U2" s="5">
         <v>0</v>
@@ -1488,43 +1488,43 @@
       </c>
       <c r="T3" s="5">
         <f>SUM($B2:T2)</f>
-        <v>2.627665390924</v>
+        <v>2.78458173865501</v>
       </c>
       <c r="U3" s="5">
         <f>SUM($B2:U2)</f>
-        <v>2.627665390924</v>
+        <v>2.78458173865501</v>
       </c>
       <c r="V3" s="5">
         <f>SUM($B2:V2)</f>
-        <v>2.627665390924</v>
+        <v>2.78458173865501</v>
       </c>
       <c r="W3" s="5">
         <f>SUM($B2:W2)</f>
-        <v>2.627665390924</v>
+        <v>2.78458173865501</v>
       </c>
       <c r="X3" s="5">
         <f>SUM($B2:X2)</f>
-        <v>2.627665390924</v>
+        <v>2.78458173865501</v>
       </c>
       <c r="Y3" s="5">
         <f>SUM($B2:Y2)</f>
-        <v>2.627665390924</v>
+        <v>2.78458173865501</v>
       </c>
       <c r="Z3" s="5">
         <f>SUM($B2:Z2)</f>
-        <v>2.627665390924</v>
+        <v>2.78458173865501</v>
       </c>
       <c r="AA3" s="5">
         <f>SUM($B2:AA2)</f>
-        <v>2.627665390924</v>
+        <v>2.78458173865501</v>
       </c>
       <c r="AB3" s="5">
         <f>SUM($B2:AB2)</f>
-        <v>2.627665390924</v>
+        <v>2.78458173865501</v>
       </c>
       <c r="AC3" s="5">
         <f>SUM($B2:AC2)</f>
-        <v>2.627665390924</v>
+        <v>2.78458173865501</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -1605,43 +1605,43 @@
       </c>
       <c r="T4" s="5">
         <f>AVERAGE($B2:T2)</f>
-        <v>0.138298178469684</v>
+        <v>0.146556933613421</v>
       </c>
       <c r="U4" s="5">
         <f>AVERAGE($B2:U2)</f>
-        <v>0.1313832695462</v>
+        <v>0.13922908693275</v>
       </c>
       <c r="V4" s="5">
         <f>AVERAGE($B2:V2)</f>
-        <v>0.125126923377334</v>
+        <v>0.132599130412143</v>
       </c>
       <c r="W4" s="5">
         <f>AVERAGE($B2:W2)</f>
-        <v>0.119439335951091</v>
+        <v>0.126571897211591</v>
       </c>
       <c r="X4" s="5">
         <f>AVERAGE($B2:X2)</f>
-        <v>0.114246321344522</v>
+        <v>0.12106877124587</v>
       </c>
       <c r="Y4" s="5">
         <f>AVERAGE($B2:Y2)</f>
-        <v>0.109486057955167</v>
+        <v>0.116024239110625</v>
       </c>
       <c r="Z4" s="5">
         <f>AVERAGE($B2:Z2)</f>
-        <v>0.10510661563696</v>
+        <v>0.1113832695462</v>
       </c>
       <c r="AA4" s="5">
         <f>AVERAGE($B2:AA2)</f>
-        <v>0.101064053497077</v>
+        <v>0.107099297640577</v>
       </c>
       <c r="AB4" s="5">
         <f>AVERAGE($B2:AB2)</f>
-        <v>0.0973209404045928</v>
+        <v>0.103132656987222</v>
       </c>
       <c r="AC4" s="5">
         <f>AVERAGE($B2:AC2)</f>
-        <v>0.0938451925330002</v>
+        <v>0.0994493478091073</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="T6" s="5">
         <f>T5-T2</f>
-        <v>0.153846153846154</v>
+        <v>-0.00307019388484656</v>
       </c>
       <c r="U6" s="5">
         <f>U5-U2</f>
@@ -2840,7 +2840,7 @@
         <v>15</v>
       </c>
       <c r="J44" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2861,25 +2861,25 @@
       </c>
       <c r="E45" s="5">
         <f>AVERAGE(F$45:F45)</f>
-        <v>0.0135593220338983</v>
+        <v>0.152542372881356</v>
       </c>
       <c r="F45" s="5">
         <f>G45/B45</f>
-        <v>0.0135593220338983</v>
+        <v>0.152542372881356</v>
       </c>
       <c r="G45" s="1">
         <f>I45-H45</f>
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="H45" s="1">
-        <v>180</v>
-      </c>
-      <c r="I45" s="8">
+        <v>225</v>
+      </c>
+      <c r="I45" s="7">
         <f>MIN($J$44*D45,J45)</f>
-        <v>184</v>
+        <v>270</v>
       </c>
       <c r="J45" s="1">
-        <v>184</v>
+        <v>295</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2887,8 +2887,8 @@
         <v>41</v>
       </c>
       <c r="B46" s="1">
-        <f>16+15</f>
-        <v>31</v>
+        <f>16+14</f>
+        <v>30</v>
       </c>
       <c r="C46" s="5">
         <f>C45</f>
@@ -2900,22 +2900,22 @@
       </c>
       <c r="E46" s="5">
         <f>AVERAGE(F$45:F46)</f>
-        <v>0.0874248223072717</v>
+        <v>0.0929378531073446</v>
       </c>
       <c r="F46" s="5">
         <f>G46/B46</f>
-        <v>0.161290322580645</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="G46" s="1">
         <f>I46-H46</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H46" s="1">
-        <v>20</v>
-      </c>
-      <c r="I46" s="7">
+        <v>25</v>
+      </c>
+      <c r="I46" s="8">
         <f>MIN($J$44*D46,J46)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J46" s="1">
         <v>26</v>
@@ -2926,7 +2926,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AC45 A46:I46 K46:AC46" formulaRange="1"/>
+    <ignoredError sqref="A1:AC1 A2:S2 U2:AC2 A3:AC43 A44:I44 K44:AC46 A45:G45 I45:I46 A46 C46:G46" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3205,10 +3205,10 @@
       </c>
       <c r="B24" s="1">
         <f>SUM(C24:E24)</f>
-        <v>184</v>
+        <v>295</v>
       </c>
       <c r="C24" s="1">
-        <v>101</v>
+        <v>212</v>
       </c>
       <c r="D24" s="1">
         <v>52</v>

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="79">
   <si>
     <t>日期</t>
   </si>
@@ -228,7 +228,13 @@
     <t>BioInfo</t>
   </si>
   <si>
+    <t>A Dual-Population Hybrid Evolutionary Algorithm for Solving the Colored Traveling Salesman Problem</t>
+  </si>
+  <si>
     <t>SigInt</t>
+  </si>
+  <si>
+    <t>An Adaptive Multi-meme Memetic Algorithm for the Prize-Collecting Generalized Minimum Spanning Tree Problem</t>
   </si>
   <si>
     <t>IC Layout</t>
@@ -2900,25 +2906,25 @@
       </c>
       <c r="E46" s="5">
         <f>AVERAGE(F$45:F46)</f>
-        <v>0.0929378531073446</v>
+        <v>0.126271186440678</v>
       </c>
       <c r="F46" s="5">
         <f>G46/B46</f>
-        <v>0.0333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="G46" s="1">
         <f>I46-H46</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H46" s="1">
         <v>25</v>
       </c>
       <c r="I46" s="8">
         <f>MIN($J$44*D46,J46)</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J46" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3098,7 +3104,9 @@
       <c r="D12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
@@ -3108,13 +3116,15 @@
         <v>464</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="2"/>
+        <v>67</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="D14" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -3126,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -3138,7 +3148,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -3150,12 +3160,12 @@
         <v>0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B18" s="1">
         <v>0</v>
@@ -3187,16 +3197,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="C23" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -3217,7 +3227,7 @@
         <v>31</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -3226,13 +3236,13 @@
       </c>
       <c r="B25" s="1">
         <f>SUM(C25:D25)</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1">
         <v>16</v>
       </c>
       <c r="D25" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6">

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="进度" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="81">
   <si>
     <t>日期</t>
   </si>
@@ -240,7 +240,13 @@
     <t>IC Layout</t>
   </si>
   <si>
+    <t>Enhanced List-Based Simulated Annealing Algorithm for Large-Scale Traveling Salesman Problem</t>
+  </si>
+  <si>
     <t>SoftTST</t>
+  </si>
+  <si>
+    <t>Low-latency Virtual Network function Scheduling Algorithm Based on Deep Reinforcement Learning</t>
   </si>
   <si>
     <t>Godot2D</t>
@@ -1374,25 +1380,25 @@
         <v>0.0695173362502559</v>
       </c>
       <c r="P2" s="5">
-        <v>0.156916347731001</v>
+        <v>0.159785932721713</v>
       </c>
       <c r="Q2" s="5">
-        <v>0.156916347731001</v>
+        <v>0.159785932721713</v>
       </c>
       <c r="R2" s="5">
-        <v>0.156916347731001</v>
+        <v>0.159785932721713</v>
       </c>
       <c r="S2" s="5">
-        <v>0.156916347731001</v>
+        <v>0.159785932721713</v>
       </c>
       <c r="T2" s="5">
-        <v>0.156916347731001</v>
+        <v>0.159785932721713</v>
       </c>
       <c r="U2" s="5">
-        <v>0</v>
+        <v>0.159785932721713</v>
       </c>
       <c r="V2" s="5">
-        <v>0</v>
+        <v>0.0412844036697248</v>
       </c>
       <c r="W2" s="5">
         <v>0</v>
@@ -1478,59 +1484,59 @@
       </c>
       <c r="P3" s="5">
         <f>SUM($B2:P2)</f>
-        <v>2.156916347731</v>
+        <v>2.15978593272171</v>
       </c>
       <c r="Q3" s="5">
         <f>SUM($B2:Q2)</f>
-        <v>2.313832695462</v>
+        <v>2.31957186544343</v>
       </c>
       <c r="R3" s="5">
         <f>SUM($B2:R2)</f>
-        <v>2.470749043193</v>
+        <v>2.47935779816514</v>
       </c>
       <c r="S3" s="5">
         <f>SUM($B2:S2)</f>
-        <v>2.627665390924</v>
+        <v>2.63914373088685</v>
       </c>
       <c r="T3" s="5">
         <f>SUM($B2:T2)</f>
-        <v>2.78458173865501</v>
+        <v>2.79892966360857</v>
       </c>
       <c r="U3" s="5">
         <f>SUM($B2:U2)</f>
-        <v>2.78458173865501</v>
+        <v>2.95871559633028</v>
       </c>
       <c r="V3" s="5">
         <f>SUM($B2:V2)</f>
-        <v>2.78458173865501</v>
+        <v>3</v>
       </c>
       <c r="W3" s="5">
         <f>SUM($B2:W2)</f>
-        <v>2.78458173865501</v>
+        <v>3</v>
       </c>
       <c r="X3" s="5">
         <f>SUM($B2:X2)</f>
-        <v>2.78458173865501</v>
+        <v>3</v>
       </c>
       <c r="Y3" s="5">
         <f>SUM($B2:Y2)</f>
-        <v>2.78458173865501</v>
+        <v>3</v>
       </c>
       <c r="Z3" s="5">
         <f>SUM($B2:Z2)</f>
-        <v>2.78458173865501</v>
+        <v>3</v>
       </c>
       <c r="AA3" s="5">
         <f>SUM($B2:AA2)</f>
-        <v>2.78458173865501</v>
+        <v>3</v>
       </c>
       <c r="AB3" s="5">
         <f>SUM($B2:AB2)</f>
-        <v>2.78458173865501</v>
+        <v>3</v>
       </c>
       <c r="AC3" s="5">
         <f>SUM($B2:AC2)</f>
-        <v>2.78458173865501</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -1595,59 +1601,59 @@
       </c>
       <c r="P4" s="5">
         <f>AVERAGE($B2:P2)</f>
-        <v>0.143794423182067</v>
+        <v>0.143985728848114</v>
       </c>
       <c r="Q4" s="5">
         <f>AVERAGE($B2:Q2)</f>
-        <v>0.144614543466375</v>
+        <v>0.144973241590214</v>
       </c>
       <c r="R4" s="5">
         <f>AVERAGE($B2:R2)</f>
-        <v>0.145338179011353</v>
+        <v>0.145844576362655</v>
       </c>
       <c r="S4" s="5">
         <f>AVERAGE($B2:S2)</f>
-        <v>0.145981410606889</v>
+        <v>0.146619096160381</v>
       </c>
       <c r="T4" s="5">
         <f>AVERAGE($B2:T2)</f>
-        <v>0.146556933613421</v>
+        <v>0.147312087558346</v>
       </c>
       <c r="U4" s="5">
         <f>AVERAGE($B2:U2)</f>
-        <v>0.13922908693275</v>
+        <v>0.147935779816514</v>
       </c>
       <c r="V4" s="5">
         <f>AVERAGE($B2:V2)</f>
-        <v>0.132599130412143</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="W4" s="5">
         <f>AVERAGE($B2:W2)</f>
-        <v>0.126571897211591</v>
+        <v>0.136363636363636</v>
       </c>
       <c r="X4" s="5">
         <f>AVERAGE($B2:X2)</f>
-        <v>0.12106877124587</v>
+        <v>0.130434782608696</v>
       </c>
       <c r="Y4" s="5">
         <f>AVERAGE($B2:Y2)</f>
-        <v>0.116024239110625</v>
+        <v>0.125</v>
       </c>
       <c r="Z4" s="5">
         <f>AVERAGE($B2:Z2)</f>
-        <v>0.1113832695462</v>
+        <v>0.12</v>
       </c>
       <c r="AA4" s="5">
         <f>AVERAGE($B2:AA2)</f>
-        <v>0.107099297640577</v>
+        <v>0.115384615384615</v>
       </c>
       <c r="AB4" s="5">
         <f>AVERAGE($B2:AB2)</f>
-        <v>0.103132656987222</v>
+        <v>0.111111111111111</v>
       </c>
       <c r="AC4" s="5">
         <f>AVERAGE($B2:AC2)</f>
-        <v>0.0994493478091073</v>
+        <v>0.107142857142857</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1829,31 +1835,31 @@
       </c>
       <c r="P6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.00307019388484656</v>
+        <v>-0.00593977887555855</v>
       </c>
       <c r="Q6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.00307019388484656</v>
+        <v>-0.00593977887555855</v>
       </c>
       <c r="R6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.00307019388484656</v>
+        <v>-0.00593977887555855</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.00307019388484656</v>
+        <v>-0.00593977887555855</v>
       </c>
       <c r="T6" s="5">
         <f>T5-T2</f>
-        <v>-0.00307019388484656</v>
+        <v>-0.00593977887555855</v>
       </c>
       <c r="U6" s="5">
         <f>U5-U2</f>
-        <v>0.153846153846154</v>
+        <v>-0.00593977887555855</v>
       </c>
       <c r="V6" s="5">
         <f>V5-V2</f>
-        <v>0.153846153846154</v>
+        <v>0.112561750176429</v>
       </c>
       <c r="W6" s="5">
         <f>W5-W2</f>
@@ -2553,7 +2559,7 @@
         <f t="shared" ref="G32:G35" si="15">I32-H32</f>
         <v>0</v>
       </c>
-      <c r="I32" s="7">
+      <c r="I32" s="8">
         <f t="shared" ref="I32:I35" si="16">MIN($J$31*D32,J32)</f>
         <v>0</v>
       </c>
@@ -2588,7 +2594,7 @@
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="I33" s="7">
+      <c r="I33" s="8">
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
@@ -2623,7 +2629,7 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I34" s="7">
+      <c r="I34" s="8">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -2648,22 +2654,22 @@
       </c>
       <c r="E35" s="5">
         <f>AVERAGE(F$32:F35)</f>
-        <v>0.0166666666666667</v>
+        <v>0.0545454545454545</v>
       </c>
       <c r="F35" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>0.151515151515152</v>
       </c>
       <c r="G35" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I35" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J35" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2846,7 +2852,7 @@
         <v>15</v>
       </c>
       <c r="J44" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2854,8 +2860,8 @@
         <v>40</v>
       </c>
       <c r="B45" s="1">
-        <f>212+52+31</f>
-        <v>295</v>
+        <f>212+52+63</f>
+        <v>327</v>
       </c>
       <c r="C45" s="5">
         <f>4/26</f>
@@ -2863,29 +2869,29 @@
       </c>
       <c r="D45" s="1">
         <f>ROUND(B45*C45,0)</f>
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E45" s="5">
         <f>AVERAGE(F$45:F45)</f>
-        <v>0.152542372881356</v>
+        <v>0.0825688073394495</v>
       </c>
       <c r="F45" s="5">
         <f>G45/B45</f>
-        <v>0.152542372881356</v>
+        <v>0.0825688073394495</v>
       </c>
       <c r="G45" s="1">
         <f>I45-H45</f>
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H45" s="1">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="I45" s="7">
         <f>MIN($J$44*D45,J45)</f>
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="J45" s="1">
-        <v>295</v>
+        <v>327</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2906,25 +2912,25 @@
       </c>
       <c r="E46" s="5">
         <f>AVERAGE(F$45:F46)</f>
-        <v>0.126271186440678</v>
+        <v>0.0412844036697248</v>
       </c>
       <c r="F46" s="5">
         <f>G46/B46</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="1">
         <f>I46-H46</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H46" s="1">
-        <v>25</v>
-      </c>
-      <c r="I46" s="8">
+        <v>30</v>
+      </c>
+      <c r="I46" s="7">
         <f>MIN($J$44*D46,J46)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J46" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2932,7 +2938,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AC1 A2:S2 U2:AC2 A3:AC43 A44:I44 K44:AC46 A45:G45 I45:I46 A46 C46:G46" formulaRange="1"/>
+    <ignoredError sqref="A1:AC1 A2:O2 W2:AC2 A3:AC31 A32:I35 K32:AC35 A36:AC43 A44:I44 K44:AC46 A45:A46 C45:G46 I45:I46" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3126,7 +3132,9 @@
       <c r="D14" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
@@ -3136,9 +3144,11 @@
         <v>0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
@@ -3148,7 +3158,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -3160,15 +3170,15 @@
         <v>0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B18" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -3197,16 +3207,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="C23" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -3215,7 +3225,7 @@
       </c>
       <c r="B24" s="1">
         <f>SUM(C24:E24)</f>
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="C24" s="1">
         <v>212</v>
@@ -3224,10 +3234,10 @@
         <v>52</v>
       </c>
       <c r="E24" s="1">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -3236,13 +3246,13 @@
       </c>
       <c r="B25" s="1">
         <f>SUM(C25:D25)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C25" s="1">
         <v>16</v>
       </c>
       <c r="D25" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:6">

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -2549,22 +2549,22 @@
       </c>
       <c r="E32" s="5">
         <f>AVERAGE(F$32:F32)</f>
-        <v>0</v>
+        <v>0.0681818181818182</v>
       </c>
       <c r="F32" s="5">
         <f t="shared" ref="F32:F35" si="14">G32/B32</f>
-        <v>0</v>
+        <v>0.0681818181818182</v>
       </c>
       <c r="G32" s="1">
         <f t="shared" ref="G32:G35" si="15">I32-H32</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I32" s="8">
         <f t="shared" ref="I32:I35" si="16">MIN($J$31*D32,J32)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J32" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="E33" s="5">
         <f>AVERAGE(F$32:F33)</f>
-        <v>0.0333333333333333</v>
+        <v>0.0674242424242424</v>
       </c>
       <c r="F33" s="5">
         <f t="shared" si="14"/>
@@ -2619,22 +2619,22 @@
       </c>
       <c r="E34" s="5">
         <f>AVERAGE(F$32:F34)</f>
-        <v>0.0222222222222222</v>
+        <v>0.0964262881984401</v>
       </c>
       <c r="F34" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>0.154430379746835</v>
       </c>
       <c r="G34" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="8">
+        <v>61</v>
+      </c>
+      <c r="I34" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="J34" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="E35" s="5">
         <f>AVERAGE(F$32:F35)</f>
-        <v>0.0545454545454545</v>
+        <v>0.110198504027618</v>
       </c>
       <c r="F35" s="5">
         <f t="shared" si="14"/>
@@ -2669,7 +2669,7 @@
         <v>10</v>
       </c>
       <c r="J35" s="1">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -3141,7 +3141,7 @@
         <v>32</v>
       </c>
       <c r="B15" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>71</v>
@@ -3167,7 +3167,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>74</v>
@@ -3178,7 +3178,7 @@
         <v>75</v>
       </c>
       <c r="B18" s="1">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:6">

--- a/FZU/PlanB/磁场转动.xlsx
+++ b/FZU/PlanB/磁场转动.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="83">
   <si>
     <t>日期</t>
   </si>
@@ -153,124 +153,130 @@
     <t>农大辅导</t>
   </si>
   <si>
+    <t>调剂准备</t>
+  </si>
+  <si>
+    <t>库的实现</t>
+  </si>
+  <si>
+    <t>页码</t>
+  </si>
+  <si>
+    <t>简历</t>
+  </si>
+  <si>
+    <t>导师</t>
+  </si>
+  <si>
+    <t>LMS</t>
+  </si>
+  <si>
+    <t>A review of visual perception technology for intelligent fruit harvesting robots</t>
+  </si>
+  <si>
+    <t>CDCGAN</t>
+  </si>
+  <si>
+    <t>AI-empowered Channel Estimation for Block-based Active IRS-enhanced Hybrid-field IoT Network</t>
+  </si>
+  <si>
+    <t>LabVIEW</t>
+  </si>
+  <si>
+    <t>GLN-LRF global learning network based on large receptive fields for hyperspectral image classification</t>
+  </si>
+  <si>
+    <t>LCD Panel</t>
+  </si>
+  <si>
+    <t>GPI-Net Gestalt-Guided Parallel Interaction Network via Orthogonal Geometric Consistency for Robust Point Cloud Registration</t>
+  </si>
+  <si>
+    <t>OpenCog</t>
+  </si>
+  <si>
+    <t>Multiple attribute group decision making based on nucleolus weight and continuous optimal distance measure</t>
+  </si>
+  <si>
+    <t>OpenNARS</t>
+  </si>
+  <si>
+    <t>Semantic Communication for Efficient Point Cloud Transmission</t>
+  </si>
+  <si>
+    <t>YOLO</t>
+  </si>
+  <si>
+    <t>Discrete comprehensive learning particle swarm optimization algorithm with Metropolis acceptance criterion for traveling salesman problem</t>
+  </si>
+  <si>
+    <t>FaceNet</t>
+  </si>
+  <si>
+    <t>Discrete pigeon-inspired optimization algorithm with Metropolis acceptance criterion for large-scale traveling salesman problem</t>
+  </si>
+  <si>
+    <t>BCI</t>
+  </si>
+  <si>
+    <t>List-based Simulated Annealing Algorithm with Hybrid Greedy Repair and Optimization Operator for 0-1 Knapsack Problem</t>
+  </si>
+  <si>
+    <t>MedImg</t>
+  </si>
+  <si>
+    <t>Noising methods with hybrid greedy repair operator for 0–1 knapsack problem</t>
+  </si>
+  <si>
+    <t>BioInfo</t>
+  </si>
+  <si>
+    <t>A Dual-Population Hybrid Evolutionary Algorithm for Solving the Colored Traveling Salesman Problem</t>
+  </si>
+  <si>
+    <t>SigInt</t>
+  </si>
+  <si>
+    <t>An Adaptive Multi-meme Memetic Algorithm for the Prize-Collecting Generalized Minimum Spanning Tree Problem</t>
+  </si>
+  <si>
+    <t>IC Layout</t>
+  </si>
+  <si>
+    <t>Enhanced List-Based Simulated Annealing Algorithm for Large-Scale Traveling Salesman Problem</t>
+  </si>
+  <si>
+    <t>SoftTST</t>
+  </si>
+  <si>
+    <t>Low-latency Virtual Network function Scheduling Algorithm Based on Deep Reinforcement Learning</t>
+  </si>
+  <si>
+    <t>Godot2D</t>
+  </si>
+  <si>
+    <t>OpenGL</t>
+  </si>
+  <si>
+    <t>三论概述</t>
+  </si>
+  <si>
+    <t>面试</t>
+  </si>
+  <si>
+    <t>上机</t>
+  </si>
+  <si>
+    <t>视频</t>
+  </si>
+  <si>
+    <t>视频#</t>
+  </si>
+  <si>
+    <t>3-8</t>
+  </si>
+  <si>
     <t>农大准备</t>
-  </si>
-  <si>
-    <t>页码</t>
-  </si>
-  <si>
-    <t>简历</t>
-  </si>
-  <si>
-    <t>导师</t>
-  </si>
-  <si>
-    <t>LMS</t>
-  </si>
-  <si>
-    <t>A review of visual perception technology for intelligent fruit harvesting robots</t>
-  </si>
-  <si>
-    <t>CDCGAN</t>
-  </si>
-  <si>
-    <t>AI-empowered Channel Estimation for Block-based Active IRS-enhanced Hybrid-field IoT Network</t>
-  </si>
-  <si>
-    <t>LabVIEW</t>
-  </si>
-  <si>
-    <t>GLN-LRF global learning network based on large receptive fields for hyperspectral image classification</t>
-  </si>
-  <si>
-    <t>LCD Panel</t>
-  </si>
-  <si>
-    <t>GPI-Net Gestalt-Guided Parallel Interaction Network via Orthogonal Geometric Consistency for Robust Point Cloud Registration</t>
-  </si>
-  <si>
-    <t>OpenCog</t>
-  </si>
-  <si>
-    <t>Multiple attribute group decision making based on nucleolus weight and continuous optimal distance measure</t>
-  </si>
-  <si>
-    <t>OpenNARS</t>
-  </si>
-  <si>
-    <t>Semantic Communication for Efficient Point Cloud Transmission</t>
-  </si>
-  <si>
-    <t>YOLO</t>
-  </si>
-  <si>
-    <t>Discrete comprehensive learning particle swarm optimization algorithm with Metropolis acceptance criterion for traveling salesman problem</t>
-  </si>
-  <si>
-    <t>FaceNet</t>
-  </si>
-  <si>
-    <t>Discrete pigeon-inspired optimization algorithm with Metropolis acceptance criterion for large-scale traveling salesman problem</t>
-  </si>
-  <si>
-    <t>BCI</t>
-  </si>
-  <si>
-    <t>List-based Simulated Annealing Algorithm with Hybrid Greedy Repair and Optimization Operator for 0-1 Knapsack Problem</t>
-  </si>
-  <si>
-    <t>MedImg</t>
-  </si>
-  <si>
-    <t>Noising methods with hybrid greedy repair operator for 0–1 knapsack problem</t>
-  </si>
-  <si>
-    <t>BioInfo</t>
-  </si>
-  <si>
-    <t>A Dual-Population Hybrid Evolutionary Algorithm for Solving the Colored Traveling Salesman Problem</t>
-  </si>
-  <si>
-    <t>SigInt</t>
-  </si>
-  <si>
-    <t>An Adaptive Multi-meme Memetic Algorithm for the Prize-Collecting Generalized Minimum Spanning Tree Problem</t>
-  </si>
-  <si>
-    <t>IC Layout</t>
-  </si>
-  <si>
-    <t>Enhanced List-Based Simulated Annealing Algorithm for Large-Scale Traveling Salesman Problem</t>
-  </si>
-  <si>
-    <t>SoftTST</t>
-  </si>
-  <si>
-    <t>Low-latency Virtual Network function Scheduling Algorithm Based on Deep Reinforcement Learning</t>
-  </si>
-  <si>
-    <t>Godot2D</t>
-  </si>
-  <si>
-    <t>OpenGL</t>
-  </si>
-  <si>
-    <t>三论概述</t>
-  </si>
-  <si>
-    <t>面试</t>
-  </si>
-  <si>
-    <t>上机</t>
-  </si>
-  <si>
-    <t>视频</t>
-  </si>
-  <si>
-    <t>视频#</t>
-  </si>
-  <si>
-    <t>3-8</t>
   </si>
 </sst>
 </file>
@@ -1238,7 +1244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="15.7777777777778" style="1" customWidth="1"/>
@@ -1401,7 +1407,7 @@
         <v>0.0412844036697248</v>
       </c>
       <c r="W2" s="5">
-        <v>0</v>
+        <v>0.156031837360951</v>
       </c>
       <c r="X2" s="5">
         <v>0</v>
@@ -1512,31 +1518,31 @@
       </c>
       <c r="W3" s="5">
         <f>SUM($B2:W2)</f>
-        <v>3</v>
+        <v>3.15603183736095</v>
       </c>
       <c r="X3" s="5">
         <f>SUM($B2:X2)</f>
-        <v>3</v>
+        <v>3.15603183736095</v>
       </c>
       <c r="Y3" s="5">
         <f>SUM($B2:Y2)</f>
-        <v>3</v>
+        <v>3.15603183736095</v>
       </c>
       <c r="Z3" s="5">
         <f>SUM($B2:Z2)</f>
-        <v>3</v>
+        <v>3.15603183736095</v>
       </c>
       <c r="AA3" s="5">
         <f>SUM($B2:AA2)</f>
-        <v>3</v>
+        <v>3.15603183736095</v>
       </c>
       <c r="AB3" s="5">
         <f>SUM($B2:AB2)</f>
-        <v>3</v>
+        <v>3.15603183736095</v>
       </c>
       <c r="AC3" s="5">
         <f>SUM($B2:AC2)</f>
-        <v>3</v>
+        <v>3.15603183736095</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -1629,31 +1635,31 @@
       </c>
       <c r="W4" s="5">
         <f>AVERAGE($B2:W2)</f>
-        <v>0.136363636363636</v>
+        <v>0.143455992607316</v>
       </c>
       <c r="X4" s="5">
         <f>AVERAGE($B2:X2)</f>
-        <v>0.130434782608696</v>
+        <v>0.137218775537433</v>
       </c>
       <c r="Y4" s="5">
         <f>AVERAGE($B2:Y2)</f>
-        <v>0.125</v>
+        <v>0.131501326556706</v>
       </c>
       <c r="Z4" s="5">
         <f>AVERAGE($B2:Z2)</f>
-        <v>0.12</v>
+        <v>0.126241273494438</v>
       </c>
       <c r="AA4" s="5">
         <f>AVERAGE($B2:AA2)</f>
-        <v>0.115384615384615</v>
+        <v>0.121385839898498</v>
       </c>
       <c r="AB4" s="5">
         <f>AVERAGE($B2:AB2)</f>
-        <v>0.111111111111111</v>
+        <v>0.116890068050406</v>
       </c>
       <c r="AC4" s="5">
         <f>AVERAGE($B2:AC2)</f>
-        <v>0.107142857142857</v>
+        <v>0.112715422762891</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1863,7 +1869,7 @@
       </c>
       <c r="W6" s="5">
         <f>W5-W2</f>
-        <v>0.153846153846154</v>
+        <v>-0.00218568351479728</v>
       </c>
       <c r="X6" s="5">
         <f>X5-X2</f>
@@ -2529,7 +2535,7 @@
         <v>15</v>
       </c>
       <c r="J31" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2549,22 +2555,25 @@
       </c>
       <c r="E32" s="5">
         <f>AVERAGE(F$32:F32)</f>
-        <v>0.0681818181818182</v>
+        <v>0.151515151515152</v>
       </c>
       <c r="F32" s="5">
         <f t="shared" ref="F32:F35" si="14">G32/B32</f>
-        <v>0.0681818181818182</v>
+        <v>0.151515151515152</v>
       </c>
       <c r="G32" s="1">
         <f t="shared" ref="G32:G35" si="15">I32-H32</f>
-        <v>9</v>
-      </c>
-      <c r="I32" s="8">
+        <v>20</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="7">
         <f t="shared" ref="I32:I35" si="16">MIN($J$31*D32,J32)</f>
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="J32" s="1">
-        <v>9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2584,22 +2593,25 @@
       </c>
       <c r="E33" s="5">
         <f>AVERAGE(F$32:F33)</f>
-        <v>0.0674242424242424</v>
+        <v>0.159090909090909</v>
       </c>
       <c r="F33" s="5">
         <f t="shared" si="14"/>
-        <v>0.0666666666666667</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="G33" s="1">
         <f t="shared" si="15"/>
-        <v>2</v>
-      </c>
-      <c r="I33" s="8">
+        <v>5</v>
+      </c>
+      <c r="H33" s="1">
+        <v>5</v>
+      </c>
+      <c r="I33" s="7">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J33" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2619,22 +2631,25 @@
       </c>
       <c r="E34" s="5">
         <f>AVERAGE(F$32:F34)</f>
-        <v>0.0964262881984401</v>
+        <v>0.152474108170311</v>
       </c>
       <c r="F34" s="5">
         <f t="shared" si="14"/>
-        <v>0.154430379746835</v>
+        <v>0.139240506329114</v>
       </c>
       <c r="G34" s="1">
         <f t="shared" si="15"/>
+        <v>55</v>
+      </c>
+      <c r="H34" s="1">
         <v>61</v>
       </c>
-      <c r="I34" s="7">
+      <c r="I34" s="8">
         <f t="shared" si="16"/>
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="J34" s="1">
-        <v>70</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2654,7 +2669,7 @@
       </c>
       <c r="E35" s="5">
         <f>AVERAGE(F$32:F35)</f>
-        <v>0.110198504027618</v>
+        <v>0.152234369006521</v>
       </c>
       <c r="F35" s="5">
         <f t="shared" si="14"/>
@@ -2664,9 +2679,12 @@
         <f t="shared" si="15"/>
         <v>10</v>
       </c>
+      <c r="H35" s="1">
+        <v>10</v>
+      </c>
       <c r="I35" s="7">
         <f t="shared" si="16"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J35" s="1">
         <v>32</v>
@@ -2931,6 +2949,81 @@
       </c>
       <c r="J46" s="1">
         <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="1">
+        <v>523</v>
+      </c>
+      <c r="C50" s="5">
+        <f>4/26</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D50" s="1">
+        <f>ROUND(B50*C50,0)</f>
+        <v>80</v>
+      </c>
+      <c r="E50" s="5">
+        <f>AVERAGE(F$50:F50)</f>
+        <v>0.0611854684512428</v>
+      </c>
+      <c r="F50" s="5">
+        <f>G50/B50</f>
+        <v>0.0611854684512428</v>
+      </c>
+      <c r="G50" s="1">
+        <f>I50-H50</f>
+        <v>32</v>
+      </c>
+      <c r="I50" s="8">
+        <f>MIN($J$49*D50,J50)</f>
+        <v>32</v>
+      </c>
+      <c r="J50" s="1">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2938,7 +3031,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AC1 A2:O2 W2:AC2 A3:AC31 A32:I35 K32:AC35 A36:AC43 A44:I44 K44:AC46 A45:A46 C45:G46 I45:I46" formulaRange="1"/>
+    <ignoredError sqref="A36:AC43 A1:AC1 A2:O2 X2:AC2 A3:AC30 A31:I31 K31:AC35 A32:G35 I32:I35 A44:I44 K44:AC46 A45 C45:G46 I45:I46" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2946,7 +3039,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="10.7777777777778" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="16384" width="10.7777777777778" style="1" customWidth="1"/>
@@ -2957,13 +3050,13 @@
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2974,10 +3067,10 @@
         <v>202</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2988,10 +3081,10 @@
         <v>390</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3002,10 +3095,10 @@
         <v>484</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3016,10 +3109,10 @@
         <v>240</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3030,10 +3123,10 @@
         <v>271</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3044,18 +3137,18 @@
         <v>278</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="D8" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3066,10 +3159,10 @@
         <v>440</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3080,10 +3173,10 @@
         <v>378</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3094,10 +3187,10 @@
         <v>209</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3108,10 +3201,10 @@
         <v>62</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3122,18 +3215,18 @@
         <v>464</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="D14" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3141,13 +3234,13 @@
         <v>32</v>
       </c>
       <c r="B15" s="1">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3155,10 +3248,10 @@
         <v>33</v>
       </c>
       <c r="B16" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -3167,15 +3260,15 @@
         <v>34</v>
       </c>
       <c r="B17" s="1">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="1">
         <v>32</v>
@@ -3207,16 +3300,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="C23" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -3237,12 +3330,12 @@
         <v>63</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="B25" s="1">
         <f>SUM(C25:D25)</f>
@@ -3257,10 +3350,18 @@
     </row>
     <row r="26" spans="1:6">
       <c r="C26" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="1">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
